--- a/research/traditional_assets/database/data/poland/poland_utility_general.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_utility_general.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07005273975681109</v>
+        <v>0.06995608955127315</v>
       </c>
       <c r="C2">
-        <v>299.6266817559662</v>
+        <v>297.8683450321221</v>
       </c>
       <c r="D2">
-        <v>295.8366817559662</v>
+        <v>297.0203450321221</v>
       </c>
       <c r="E2">
-        <v>-113.6</v>
+        <v>-110.658</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.942</v>
       </c>
       <c r="G2">
         <v>3.79</v>
@@ -1445,28 +1445,28 @@
         <v>81</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1479826</v>
       </c>
       <c r="N2">
-        <v>81</v>
+        <v>80.85201739999999</v>
       </c>
       <c r="O2">
-        <v>15.39</v>
+        <v>15.361883306</v>
       </c>
       <c r="P2">
-        <v>65.61</v>
+        <v>65.490134094</v>
       </c>
       <c r="Q2">
-        <v>121.11</v>
+        <v>120.990134094</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07005273975681109</v>
+        <v>0.07025117126391227</v>
       </c>
       <c r="T2">
-        <v>0.4441974458563936</v>
+        <v>0.4478317885952187</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>547.3616492749824</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06995608955127315</v>
+        <v>0.0698594393457352</v>
       </c>
       <c r="C3">
-        <v>297.8683450321221</v>
+        <v>296.1195181972897</v>
       </c>
       <c r="D3">
-        <v>297.0203450321221</v>
+        <v>298.2135181972897</v>
       </c>
       <c r="E3">
-        <v>-110.658</v>
+        <v>-107.716</v>
       </c>
       <c r="F3">
-        <v>2.942</v>
+        <v>5.883999999999999</v>
       </c>
       <c r="G3">
         <v>3.79</v>
@@ -1527,28 +1527,28 @@
         <v>81</v>
       </c>
       <c r="M3">
-        <v>0.1479826</v>
+        <v>0.2959652</v>
       </c>
       <c r="N3">
-        <v>80.85201739999999</v>
+        <v>80.7040348</v>
       </c>
       <c r="O3">
-        <v>15.361883306</v>
+        <v>15.333766612</v>
       </c>
       <c r="P3">
-        <v>65.490134094</v>
+        <v>65.370268188</v>
       </c>
       <c r="Q3">
-        <v>120.990134094</v>
+        <v>120.870268188</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07025117126391227</v>
+        <v>0.07045365239360735</v>
       </c>
       <c r="T3">
-        <v>0.4478317885952187</v>
+        <v>0.4515403015940198</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>547.3616492749824</v>
+        <v>273.6808246374912</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0698594393457352</v>
+        <v>0.06976278914019726</v>
       </c>
       <c r="C4">
-        <v>296.1195181972897</v>
+        <v>294.3803163214701</v>
       </c>
       <c r="D4">
-        <v>298.2135181972897</v>
+        <v>299.4163163214701</v>
       </c>
       <c r="E4">
-        <v>-107.716</v>
+        <v>-104.774</v>
       </c>
       <c r="F4">
-        <v>5.883999999999999</v>
+        <v>8.825999999999999</v>
       </c>
       <c r="G4">
         <v>3.79</v>
@@ -1609,28 +1609,28 @@
         <v>81</v>
       </c>
       <c r="M4">
-        <v>0.2959652</v>
+        <v>0.4439477999999999</v>
       </c>
       <c r="N4">
-        <v>80.7040348</v>
+        <v>80.5560522</v>
       </c>
       <c r="O4">
-        <v>15.333766612</v>
+        <v>15.305649918</v>
       </c>
       <c r="P4">
-        <v>65.370268188</v>
+        <v>65.250402282</v>
       </c>
       <c r="Q4">
-        <v>120.870268188</v>
+        <v>120.750402282</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07045365239360735</v>
+        <v>0.07066030839195594</v>
       </c>
       <c r="T4">
-        <v>0.4515403015940198</v>
+        <v>0.4553252787783632</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>273.6808246374912</v>
+        <v>182.4538830916608</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06976278914019726</v>
+        <v>0.06966613893465931</v>
       </c>
       <c r="C5">
-        <v>294.3803163214701</v>
+        <v>292.6508563386516</v>
       </c>
       <c r="D5">
-        <v>299.4163163214701</v>
+        <v>300.6288563386515</v>
       </c>
       <c r="E5">
-        <v>-104.774</v>
+        <v>-101.832</v>
       </c>
       <c r="F5">
-        <v>8.825999999999999</v>
+        <v>11.768</v>
       </c>
       <c r="G5">
         <v>3.79</v>
@@ -1691,28 +1691,28 @@
         <v>81</v>
       </c>
       <c r="M5">
-        <v>0.4439477999999999</v>
+        <v>0.5919304</v>
       </c>
       <c r="N5">
-        <v>80.5560522</v>
+        <v>80.4080696</v>
       </c>
       <c r="O5">
-        <v>15.305649918</v>
+        <v>15.277533224</v>
       </c>
       <c r="P5">
-        <v>65.250402282</v>
+        <v>65.13053637600001</v>
       </c>
       <c r="Q5">
-        <v>120.750402282</v>
+        <v>120.630536376</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07066030839195594</v>
+        <v>0.07087126972360346</v>
       </c>
       <c r="T5">
-        <v>0.4553252787783632</v>
+        <v>0.4591891096540469</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>182.4538830916608</v>
+        <v>136.8404123187456</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06966613893465931</v>
+        <v>0.06956948872912137</v>
       </c>
       <c r="C6">
-        <v>292.6508563386516</v>
+        <v>290.9312570847041</v>
       </c>
       <c r="D6">
-        <v>300.6288563386515</v>
+        <v>301.8512570847041</v>
       </c>
       <c r="E6">
-        <v>-101.832</v>
+        <v>-98.88999999999999</v>
       </c>
       <c r="F6">
-        <v>11.768</v>
+        <v>14.71</v>
       </c>
       <c r="G6">
         <v>3.79</v>
@@ -1773,28 +1773,28 @@
         <v>81</v>
       </c>
       <c r="M6">
-        <v>0.5919304</v>
+        <v>0.739913</v>
       </c>
       <c r="N6">
-        <v>80.4080696</v>
+        <v>80.260087</v>
       </c>
       <c r="O6">
-        <v>15.277533224</v>
+        <v>15.24941653</v>
       </c>
       <c r="P6">
-        <v>65.13053637600001</v>
+        <v>65.01067046999999</v>
       </c>
       <c r="Q6">
-        <v>120.630536376</v>
+        <v>120.51067047</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07087126972360346</v>
+        <v>0.07108667234644356</v>
       </c>
       <c r="T6">
-        <v>0.4591891096540469</v>
+        <v>0.4631342843376399</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>136.8404123187456</v>
+        <v>109.4723298549965</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06956948872912137</v>
+        <v>0.06947283852358344</v>
       </c>
       <c r="C7">
-        <v>290.9312570847041</v>
+        <v>289.2216393362054</v>
       </c>
       <c r="D7">
-        <v>301.8512570847041</v>
+        <v>303.0836393362054</v>
       </c>
       <c r="E7">
-        <v>-98.88999999999999</v>
+        <v>-95.94799999999998</v>
       </c>
       <c r="F7">
-        <v>14.71</v>
+        <v>17.652</v>
       </c>
       <c r="G7">
         <v>3.79</v>
@@ -1855,28 +1855,28 @@
         <v>81</v>
       </c>
       <c r="M7">
-        <v>0.739913</v>
+        <v>0.8878956</v>
       </c>
       <c r="N7">
-        <v>80.260087</v>
+        <v>80.11210440000001</v>
       </c>
       <c r="O7">
-        <v>15.24941653</v>
+        <v>15.221299836</v>
       </c>
       <c r="P7">
-        <v>65.01067046999999</v>
+        <v>64.89080456400001</v>
       </c>
       <c r="Q7">
-        <v>120.51067047</v>
+        <v>120.390804564</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07108667234644356</v>
+        <v>0.07130665800381217</v>
       </c>
       <c r="T7">
-        <v>0.4631342843376399</v>
+        <v>0.4671633989081178</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>109.4723298549965</v>
+        <v>91.2269415458304</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06947283852358344</v>
+        <v>0.0693761883180455</v>
       </c>
       <c r="C8">
-        <v>289.2216393362054</v>
+        <v>287.5221258502196</v>
       </c>
       <c r="D8">
-        <v>303.0836393362054</v>
+        <v>304.3261258502196</v>
       </c>
       <c r="E8">
-        <v>-95.94799999999998</v>
+        <v>-93.00599999999999</v>
       </c>
       <c r="F8">
-        <v>17.652</v>
+        <v>20.594</v>
       </c>
       <c r="G8">
         <v>3.79</v>
@@ -1937,28 +1937,28 @@
         <v>81</v>
       </c>
       <c r="M8">
-        <v>0.8878955999999998</v>
+        <v>1.0358782</v>
       </c>
       <c r="N8">
-        <v>80.11210440000001</v>
+        <v>79.9641218</v>
       </c>
       <c r="O8">
-        <v>15.221299836</v>
+        <v>15.193183142</v>
       </c>
       <c r="P8">
-        <v>64.89080456400001</v>
+        <v>64.77093865800001</v>
       </c>
       <c r="Q8">
-        <v>120.390804564</v>
+        <v>120.270938658</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07130665800381217</v>
+        <v>0.07153137453553279</v>
       </c>
       <c r="T8">
-        <v>0.4671633989081178</v>
+        <v>0.4712791611037673</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>91.22694154583041</v>
+        <v>78.1945213249975</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0693761883180455</v>
+        <v>0.06927953811250756</v>
       </c>
       <c r="C9">
-        <v>287.5221258502196</v>
+        <v>285.8328414050592</v>
       </c>
       <c r="D9">
-        <v>304.3261258502196</v>
+        <v>305.5788414050592</v>
       </c>
       <c r="E9">
-        <v>-93.00599999999997</v>
+        <v>-90.06399999999998</v>
       </c>
       <c r="F9">
-        <v>20.594</v>
+        <v>23.536</v>
       </c>
       <c r="G9">
         <v>3.79</v>
@@ -2019,28 +2019,28 @@
         <v>81</v>
       </c>
       <c r="M9">
-        <v>1.0358782</v>
+        <v>1.1838608</v>
       </c>
       <c r="N9">
-        <v>79.9641218</v>
+        <v>79.81613919999999</v>
       </c>
       <c r="O9">
-        <v>15.193183142</v>
+        <v>15.165066448</v>
       </c>
       <c r="P9">
-        <v>64.77093865800001</v>
+        <v>64.65107275199999</v>
       </c>
       <c r="Q9">
-        <v>120.270938658</v>
+        <v>120.151072752</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07153137453553279</v>
+        <v>0.07176097620924735</v>
       </c>
       <c r="T9">
-        <v>0.4712791611037673</v>
+        <v>0.4754843963906266</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>78.19452132499748</v>
+        <v>68.4202061593728</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06927953811250756</v>
+        <v>0.06918288790696961</v>
       </c>
       <c r="C10">
-        <v>285.8328414050592</v>
+        <v>284.1539128420584</v>
       </c>
       <c r="D10">
-        <v>305.5788414050592</v>
+        <v>306.8419128420584</v>
       </c>
       <c r="E10">
-        <v>-90.06399999999998</v>
+        <v>-87.12199999999999</v>
       </c>
       <c r="F10">
-        <v>23.536</v>
+        <v>26.478</v>
       </c>
       <c r="G10">
         <v>3.79</v>
@@ -2101,28 +2101,28 @@
         <v>81</v>
       </c>
       <c r="M10">
-        <v>1.1838608</v>
+        <v>1.3318434</v>
       </c>
       <c r="N10">
-        <v>79.81613919999999</v>
+        <v>79.6681566</v>
       </c>
       <c r="O10">
-        <v>15.165066448</v>
+        <v>15.136949754</v>
       </c>
       <c r="P10">
-        <v>64.65107275199999</v>
+        <v>64.531206846</v>
       </c>
       <c r="Q10">
-        <v>120.151072752</v>
+        <v>120.031206846</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07176097620924735</v>
+        <v>0.07199562407359297</v>
       </c>
       <c r="T10">
-        <v>0.4754843963906266</v>
+        <v>0.4797820544310432</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>68.4202061593728</v>
+        <v>60.8179610305536</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06918288790696961</v>
+        <v>0.06908623770143167</v>
       </c>
       <c r="C11">
-        <v>284.1539128420584</v>
+        <v>282.4854691083854</v>
       </c>
       <c r="D11">
-        <v>306.8419128420584</v>
+        <v>308.1154691083854</v>
       </c>
       <c r="E11">
-        <v>-87.12199999999999</v>
+        <v>-84.17999999999998</v>
       </c>
       <c r="F11">
-        <v>26.478</v>
+        <v>29.42</v>
       </c>
       <c r="G11">
         <v>3.79</v>
@@ -2183,28 +2183,28 @@
         <v>81</v>
       </c>
       <c r="M11">
-        <v>1.3318434</v>
+        <v>1.479826</v>
       </c>
       <c r="N11">
-        <v>79.6681566</v>
+        <v>79.520174</v>
       </c>
       <c r="O11">
-        <v>15.136949754</v>
+        <v>15.10883306</v>
       </c>
       <c r="P11">
-        <v>64.531206846</v>
+        <v>64.41134094</v>
       </c>
       <c r="Q11">
-        <v>120.031206846</v>
+        <v>119.91134094</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07199562407359297</v>
+        <v>0.07223548633492408</v>
       </c>
       <c r="T11">
-        <v>0.4797820544310432</v>
+        <v>0.4841752159834691</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>60.8179610305536</v>
+        <v>54.73616492749824</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06908623770143167</v>
+        <v>0.06898958749589373</v>
       </c>
       <c r="C12">
-        <v>282.4854691083854</v>
+        <v>280.8276413009273</v>
       </c>
       <c r="D12">
-        <v>308.1154691083854</v>
+        <v>309.3996413009273</v>
       </c>
       <c r="E12">
-        <v>-84.17999999999998</v>
+        <v>-81.23799999999997</v>
       </c>
       <c r="F12">
-        <v>29.42</v>
+        <v>32.362</v>
       </c>
       <c r="G12">
         <v>3.79</v>
@@ -2265,28 +2265,28 @@
         <v>81</v>
       </c>
       <c r="M12">
-        <v>1.479826</v>
+        <v>1.6278086</v>
       </c>
       <c r="N12">
-        <v>79.520174</v>
+        <v>79.37219140000001</v>
       </c>
       <c r="O12">
-        <v>15.10883306</v>
+        <v>15.080716366</v>
       </c>
       <c r="P12">
-        <v>64.41134094</v>
+        <v>64.291475034</v>
       </c>
       <c r="Q12">
-        <v>119.91134094</v>
+        <v>119.791475034</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07223548633492408</v>
+        <v>0.07248073875943116</v>
       </c>
       <c r="T12">
-        <v>0.4841752159834691</v>
+        <v>0.4886671002674101</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>54.73616492749823</v>
+        <v>49.76014993408931</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06898958749589373</v>
+        <v>0.0688929372903558</v>
       </c>
       <c r="C13">
-        <v>280.8276413009273</v>
+        <v>279.1805627112751</v>
       </c>
       <c r="D13">
-        <v>309.3996413009273</v>
+        <v>310.6945627112751</v>
       </c>
       <c r="E13">
-        <v>-81.23799999999997</v>
+        <v>-78.29599999999999</v>
       </c>
       <c r="F13">
-        <v>32.362</v>
+        <v>35.30399999999999</v>
       </c>
       <c r="G13">
         <v>3.79</v>
@@ -2347,28 +2347,28 @@
         <v>81</v>
       </c>
       <c r="M13">
-        <v>1.6278086</v>
+        <v>1.7757912</v>
       </c>
       <c r="N13">
-        <v>79.37219140000001</v>
+        <v>79.2242088</v>
       </c>
       <c r="O13">
-        <v>15.080716366</v>
+        <v>15.052599672</v>
       </c>
       <c r="P13">
-        <v>64.291475034</v>
+        <v>64.171609128</v>
       </c>
       <c r="Q13">
-        <v>119.791475034</v>
+        <v>119.671609128</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07248073875943116</v>
+        <v>0.07273156510267703</v>
       </c>
       <c r="T13">
-        <v>0.4886671002674101</v>
+        <v>0.4932610728305316</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>49.76014993408931</v>
+        <v>45.61347077291521</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0688929372903558</v>
+        <v>0.06879628708481786</v>
       </c>
       <c r="C14">
-        <v>279.1805627112751</v>
+        <v>277.5443688718439</v>
       </c>
       <c r="D14">
-        <v>310.6945627112751</v>
+        <v>312.0003688718439</v>
       </c>
       <c r="E14">
-        <v>-78.29599999999999</v>
+        <v>-75.35399999999998</v>
       </c>
       <c r="F14">
-        <v>35.30399999999999</v>
+        <v>38.246</v>
       </c>
       <c r="G14">
         <v>3.79</v>
@@ -2429,28 +2429,28 @@
         <v>81</v>
       </c>
       <c r="M14">
-        <v>1.7757912</v>
+        <v>1.9237738</v>
       </c>
       <c r="N14">
-        <v>79.2242088</v>
+        <v>79.07622619999999</v>
       </c>
       <c r="O14">
-        <v>15.052599672</v>
+        <v>15.024482978</v>
       </c>
       <c r="P14">
-        <v>64.171609128</v>
+        <v>64.051743222</v>
       </c>
       <c r="Q14">
-        <v>119.671609128</v>
+        <v>119.551743222</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07273156510267703</v>
+        <v>0.07298815756875615</v>
       </c>
       <c r="T14">
-        <v>0.4932610728305316</v>
+        <v>0.4979606539583227</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>45.61347077291521</v>
+        <v>42.10474225192171</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06879628708481786</v>
+        <v>0.06869963687927992</v>
       </c>
       <c r="C15">
-        <v>277.5443688718439</v>
+        <v>275.9191976031615</v>
       </c>
       <c r="D15">
-        <v>312.0003688718439</v>
+        <v>313.3171976031614</v>
       </c>
       <c r="E15">
-        <v>-75.35399999999998</v>
+        <v>-72.41199999999998</v>
       </c>
       <c r="F15">
-        <v>38.246</v>
+        <v>41.188</v>
       </c>
       <c r="G15">
         <v>3.79</v>
@@ -2511,28 +2511,28 @@
         <v>81</v>
       </c>
       <c r="M15">
-        <v>1.9237738</v>
+        <v>2.0717564</v>
       </c>
       <c r="N15">
-        <v>79.07622619999999</v>
+        <v>78.9282436</v>
       </c>
       <c r="O15">
-        <v>15.024482978</v>
+        <v>14.996366284</v>
       </c>
       <c r="P15">
-        <v>64.051743222</v>
+        <v>63.931877316</v>
       </c>
       <c r="Q15">
-        <v>119.551743222</v>
+        <v>119.431877316</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07298815756875615</v>
+        <v>0.07325071730148827</v>
       </c>
       <c r="T15">
-        <v>0.4979606539583227</v>
+        <v>0.5027695276704809</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>42.10474225192171</v>
+        <v>39.09726066249874</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06869963687927992</v>
+        <v>0.06860298667374197</v>
       </c>
       <c r="C16">
-        <v>275.9191976031615</v>
+        <v>274.3051890623589</v>
       </c>
       <c r="D16">
-        <v>313.3171976031614</v>
+        <v>314.6451890623588</v>
       </c>
       <c r="E16">
-        <v>-72.41199999999998</v>
+        <v>-69.46999999999997</v>
       </c>
       <c r="F16">
-        <v>41.188</v>
+        <v>44.13</v>
       </c>
       <c r="G16">
         <v>3.79</v>
@@ -2593,28 +2593,28 @@
         <v>81</v>
       </c>
       <c r="M16">
-        <v>2.0717564</v>
+        <v>2.219739</v>
       </c>
       <c r="N16">
-        <v>78.9282436</v>
+        <v>78.780261</v>
       </c>
       <c r="O16">
-        <v>14.996366284</v>
+        <v>14.96824959</v>
       </c>
       <c r="P16">
-        <v>63.931877316</v>
+        <v>63.81201141</v>
       </c>
       <c r="Q16">
-        <v>119.431877316</v>
+        <v>119.31201141</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07325071730148827</v>
+        <v>0.07351945491028467</v>
       </c>
       <c r="T16">
-        <v>0.5027695276704809</v>
+        <v>0.507691551352337</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>39.09726066249874</v>
+        <v>36.49077661833215</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06860298667374197</v>
+        <v>0.06850633646820402</v>
       </c>
       <c r="C17">
-        <v>274.3051890623589</v>
+        <v>272.7024857928988</v>
       </c>
       <c r="D17">
-        <v>314.6451890623588</v>
+        <v>315.9844857928987</v>
       </c>
       <c r="E17">
-        <v>-69.46999999999998</v>
+        <v>-66.52799999999999</v>
       </c>
       <c r="F17">
-        <v>44.13</v>
+        <v>47.072</v>
       </c>
       <c r="G17">
         <v>3.79</v>
@@ -2675,28 +2675,28 @@
         <v>81</v>
       </c>
       <c r="M17">
-        <v>2.219739</v>
+        <v>2.3677216</v>
       </c>
       <c r="N17">
-        <v>78.780261</v>
+        <v>78.6322784</v>
       </c>
       <c r="O17">
-        <v>14.96824959</v>
+        <v>14.940132896</v>
       </c>
       <c r="P17">
-        <v>63.81201141</v>
+        <v>63.692145504</v>
       </c>
       <c r="Q17">
-        <v>119.31201141</v>
+        <v>119.192145504</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07351945491028467</v>
+        <v>0.07379459103357622</v>
       </c>
       <c r="T17">
-        <v>0.507691551352337</v>
+        <v>0.5127307660742373</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>36.49077661833216</v>
+        <v>34.2101030796864</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06850633646820402</v>
+        <v>0.06840968626266608</v>
       </c>
       <c r="C18">
-        <v>272.7024857928988</v>
+        <v>271.1112327755807</v>
       </c>
       <c r="D18">
-        <v>315.9844857928987</v>
+        <v>317.3352327755807</v>
       </c>
       <c r="E18">
-        <v>-66.52799999999999</v>
+        <v>-63.58599999999998</v>
       </c>
       <c r="F18">
-        <v>47.072</v>
+        <v>50.014</v>
       </c>
       <c r="G18">
         <v>3.79</v>
@@ -2757,28 +2757,28 @@
         <v>81</v>
       </c>
       <c r="M18">
-        <v>2.3677216</v>
+        <v>2.5157042</v>
       </c>
       <c r="N18">
-        <v>78.6322784</v>
+        <v>78.4842958</v>
       </c>
       <c r="O18">
-        <v>14.940132896</v>
+        <v>14.912016202</v>
       </c>
       <c r="P18">
-        <v>63.692145504</v>
+        <v>63.57227959799999</v>
       </c>
       <c r="Q18">
-        <v>119.192145504</v>
+        <v>119.072279598</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07379459103357622</v>
+        <v>0.07407635694297118</v>
       </c>
       <c r="T18">
-        <v>0.5127307660742373</v>
+        <v>0.5178914076569062</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>34.2101030796864</v>
+        <v>32.19774407499896</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06840968626266608</v>
+        <v>0.06831303605712814</v>
       </c>
       <c r="C19">
-        <v>271.1112327755807</v>
+        <v>269.53157748086</v>
       </c>
       <c r="D19">
-        <v>317.3352327755807</v>
+        <v>318.69757748086</v>
       </c>
       <c r="E19">
-        <v>-63.58599999999998</v>
+        <v>-60.64399999999998</v>
       </c>
       <c r="F19">
-        <v>50.014</v>
+        <v>52.956</v>
       </c>
       <c r="G19">
         <v>3.79</v>
@@ -2839,28 +2839,28 @@
         <v>81</v>
       </c>
       <c r="M19">
-        <v>2.5157042</v>
+        <v>2.6636868</v>
       </c>
       <c r="N19">
-        <v>78.4842958</v>
+        <v>78.33631320000001</v>
       </c>
       <c r="O19">
-        <v>14.912016202</v>
+        <v>14.883899508</v>
       </c>
       <c r="P19">
-        <v>63.57227959799999</v>
+        <v>63.45241369200001</v>
       </c>
       <c r="Q19">
-        <v>119.072279598</v>
+        <v>118.952413692</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07407635694297118</v>
+        <v>0.07436499519161968</v>
       </c>
       <c r="T19">
-        <v>0.5178914076569062</v>
+        <v>0.5231779185464694</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>32.19774407499896</v>
+        <v>30.4089805152768</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06831303605712814</v>
+        <v>0.06821638585159021</v>
       </c>
       <c r="C20">
-        <v>269.53157748086</v>
+        <v>267.9636699225183</v>
       </c>
       <c r="D20">
-        <v>318.69757748086</v>
+        <v>320.0716699225183</v>
       </c>
       <c r="E20">
-        <v>-60.64399999999998</v>
+        <v>-57.70199999999998</v>
       </c>
       <c r="F20">
-        <v>52.956</v>
+        <v>55.898</v>
       </c>
       <c r="G20">
         <v>3.79</v>
@@ -2921,28 +2921,28 @@
         <v>81</v>
       </c>
       <c r="M20">
-        <v>2.6636868</v>
+        <v>2.8116694</v>
       </c>
       <c r="N20">
-        <v>78.33631320000001</v>
+        <v>78.1883306</v>
       </c>
       <c r="O20">
-        <v>14.883899508</v>
+        <v>14.855782814</v>
       </c>
       <c r="P20">
-        <v>63.45241369200001</v>
+        <v>63.332547786</v>
       </c>
       <c r="Q20">
-        <v>118.952413692</v>
+        <v>118.832547786</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07436499519161968</v>
+        <v>0.07466076031060519</v>
       </c>
       <c r="T20">
-        <v>0.5231779185464694</v>
+        <v>0.5285949605691084</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>30.4089805152768</v>
+        <v>28.80850785657802</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06821638585159021</v>
+        <v>0.06811973564605227</v>
       </c>
       <c r="C21">
-        <v>267.9636699225183</v>
+        <v>266.4076627127311</v>
       </c>
       <c r="D21">
-        <v>320.0716699225183</v>
+        <v>321.4576627127311</v>
       </c>
       <c r="E21">
-        <v>-57.70199999999998</v>
+        <v>-54.75999999999998</v>
       </c>
       <c r="F21">
-        <v>55.898</v>
+        <v>58.84</v>
       </c>
       <c r="G21">
         <v>3.79</v>
@@ -3003,28 +3003,28 @@
         <v>81</v>
       </c>
       <c r="M21">
-        <v>2.8116694</v>
+        <v>2.959652</v>
       </c>
       <c r="N21">
-        <v>78.1883306</v>
+        <v>78.04034799999999</v>
       </c>
       <c r="O21">
-        <v>14.855782814</v>
+        <v>14.82766612</v>
       </c>
       <c r="P21">
-        <v>63.332547786</v>
+        <v>63.21268187999999</v>
       </c>
       <c r="Q21">
-        <v>118.832547786</v>
+        <v>118.71268188</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07466076031060519</v>
+        <v>0.07496391955756533</v>
       </c>
       <c r="T21">
-        <v>0.5285949605691084</v>
+        <v>0.5341474286423135</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>28.80850785657802</v>
+        <v>27.36808246374911</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06811973564605227</v>
+        <v>0.06802308544051433</v>
       </c>
       <c r="C22">
-        <v>266.4076627127311</v>
+        <v>264.8637111185699</v>
       </c>
       <c r="D22">
-        <v>321.4576627127311</v>
+        <v>322.8557111185699</v>
       </c>
       <c r="E22">
-        <v>-54.75999999999998</v>
+        <v>-51.81799999999998</v>
       </c>
       <c r="F22">
-        <v>58.84</v>
+        <v>61.782</v>
       </c>
       <c r="G22">
         <v>3.79</v>
@@ -3085,28 +3085,28 @@
         <v>81</v>
       </c>
       <c r="M22">
-        <v>2.959652</v>
+        <v>3.1076346</v>
       </c>
       <c r="N22">
-        <v>78.04034799999999</v>
+        <v>77.8923654</v>
       </c>
       <c r="O22">
-        <v>14.82766612</v>
+        <v>14.799549426</v>
       </c>
       <c r="P22">
-        <v>63.21268187999999</v>
+        <v>63.092815974</v>
       </c>
       <c r="Q22">
-        <v>118.71268188</v>
+        <v>118.592815974</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07496391955756533</v>
+        <v>0.07527475372217003</v>
       </c>
       <c r="T22">
-        <v>0.5341474286423135</v>
+        <v>0.5398404655274982</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>27.36808246374911</v>
+        <v>26.06484044166583</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06802308544051433</v>
+        <v>0.06792643523497638</v>
       </c>
       <c r="C23">
-        <v>264.8637111185699</v>
+        <v>263.3319731199874</v>
       </c>
       <c r="D23">
-        <v>322.8557111185699</v>
+        <v>324.2659731199873</v>
       </c>
       <c r="E23">
-        <v>-51.81799999999998</v>
+        <v>-48.87599999999998</v>
       </c>
       <c r="F23">
-        <v>61.782</v>
+        <v>64.724</v>
       </c>
       <c r="G23">
         <v>3.79</v>
@@ -3167,28 +3167,28 @@
         <v>81</v>
       </c>
       <c r="M23">
-        <v>3.107634599999999</v>
+        <v>3.2556172</v>
       </c>
       <c r="N23">
-        <v>77.8923654</v>
+        <v>77.7443828</v>
       </c>
       <c r="O23">
-        <v>14.799549426</v>
+        <v>14.771432732</v>
       </c>
       <c r="P23">
-        <v>63.092815974</v>
+        <v>62.972950068</v>
       </c>
       <c r="Q23">
-        <v>118.592815974</v>
+        <v>118.472950068</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07527475372217003</v>
+        <v>0.07559355799355946</v>
       </c>
       <c r="T23">
-        <v>0.5398404655274982</v>
+        <v>0.5456794777174313</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>26.06484044166583</v>
+        <v>24.88007496704465</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06792643523497638</v>
+        <v>0.06782978502943844</v>
       </c>
       <c r="C24">
-        <v>263.3319731199874</v>
+        <v>261.8126094693264</v>
       </c>
       <c r="D24">
-        <v>324.2659731199873</v>
+        <v>325.6886094693264</v>
       </c>
       <c r="E24">
-        <v>-48.87599999999998</v>
+        <v>-45.93399999999998</v>
       </c>
       <c r="F24">
-        <v>64.724</v>
+        <v>67.666</v>
       </c>
       <c r="G24">
         <v>3.79</v>
@@ -3249,28 +3249,28 @@
         <v>81</v>
       </c>
       <c r="M24">
-        <v>3.2556172</v>
+        <v>3.4035998</v>
       </c>
       <c r="N24">
-        <v>77.7443828</v>
+        <v>77.59640020000001</v>
       </c>
       <c r="O24">
-        <v>14.771432732</v>
+        <v>14.743316038</v>
       </c>
       <c r="P24">
-        <v>62.972950068</v>
+        <v>62.853084162</v>
       </c>
       <c r="Q24">
-        <v>118.472950068</v>
+        <v>118.353084162</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07559355799355946</v>
+        <v>0.07592064289537459</v>
       </c>
       <c r="T24">
-        <v>0.5456794777174313</v>
+        <v>0.5516701525616483</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>24.88007496704465</v>
+        <v>23.79833257717315</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06782978502943844</v>
+        <v>0.0677331348239005</v>
       </c>
       <c r="C25">
-        <v>261.8126094693264</v>
+        <v>260.3057837524059</v>
       </c>
       <c r="D25">
-        <v>325.6886094693264</v>
+        <v>327.1237837524059</v>
       </c>
       <c r="E25">
-        <v>-45.93399999999998</v>
+        <v>-42.99199999999998</v>
       </c>
       <c r="F25">
-        <v>67.666</v>
+        <v>70.608</v>
       </c>
       <c r="G25">
         <v>3.79</v>
@@ -3331,28 +3331,28 @@
         <v>81</v>
       </c>
       <c r="M25">
-        <v>3.4035998</v>
+        <v>3.5515824</v>
       </c>
       <c r="N25">
-        <v>77.59640020000001</v>
+        <v>77.4484176</v>
       </c>
       <c r="O25">
-        <v>14.743316038</v>
+        <v>14.715199344</v>
       </c>
       <c r="P25">
-        <v>62.853084162</v>
+        <v>62.733218256</v>
       </c>
       <c r="Q25">
-        <v>118.353084162</v>
+        <v>118.233218256</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07592064289537459</v>
+        <v>0.07625633529460592</v>
       </c>
       <c r="T25">
-        <v>0.5516701525616483</v>
+        <v>0.5578184767438712</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>23.79833257717315</v>
+        <v>22.8067353864576</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0677331348239005</v>
+        <v>0.06763648461836255</v>
       </c>
       <c r="C26">
-        <v>260.3057837524059</v>
+        <v>258.8116624512252</v>
       </c>
       <c r="D26">
-        <v>327.1237837524059</v>
+        <v>328.5716624512252</v>
       </c>
       <c r="E26">
-        <v>-42.99199999999999</v>
+        <v>-40.04999999999998</v>
       </c>
       <c r="F26">
-        <v>70.60799999999999</v>
+        <v>73.55</v>
       </c>
       <c r="G26">
         <v>3.79</v>
@@ -3413,28 +3413,28 @@
         <v>81</v>
       </c>
       <c r="M26">
-        <v>3.551582399999999</v>
+        <v>3.699565</v>
       </c>
       <c r="N26">
-        <v>77.4484176</v>
+        <v>77.30043499999999</v>
       </c>
       <c r="O26">
-        <v>14.715199344</v>
+        <v>14.68708265</v>
       </c>
       <c r="P26">
-        <v>62.733218256</v>
+        <v>62.61335234999999</v>
       </c>
       <c r="Q26">
-        <v>118.233218256</v>
+        <v>118.11335235</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07625633529460592</v>
+        <v>0.07660097949115008</v>
       </c>
       <c r="T26">
-        <v>0.5578184767438712</v>
+        <v>0.56413075623762</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>22.8067353864576</v>
+        <v>21.89446597099929</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06763648461836255</v>
+        <v>0.06753983441282461</v>
       </c>
       <c r="C27">
-        <v>258.8116624512252</v>
+        <v>257.330415008343</v>
       </c>
       <c r="D27">
-        <v>328.5716624512252</v>
+        <v>330.032415008343</v>
       </c>
       <c r="E27">
-        <v>-40.04999999999998</v>
+        <v>-37.10799999999998</v>
       </c>
       <c r="F27">
-        <v>73.55</v>
+        <v>76.492</v>
       </c>
       <c r="G27">
         <v>3.79</v>
@@ -3495,28 +3495,28 @@
         <v>81</v>
       </c>
       <c r="M27">
-        <v>3.699565</v>
+        <v>3.8475476</v>
       </c>
       <c r="N27">
-        <v>77.30043499999999</v>
+        <v>77.1524524</v>
       </c>
       <c r="O27">
-        <v>14.68708265</v>
+        <v>14.658965956</v>
       </c>
       <c r="P27">
-        <v>62.61335234999999</v>
+        <v>62.493486444</v>
       </c>
       <c r="Q27">
-        <v>118.11335235</v>
+        <v>117.993486444</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07660097949115008</v>
+        <v>0.07695493839570894</v>
       </c>
       <c r="T27">
-        <v>0.56413075623762</v>
+        <v>0.5706136378798484</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>21.89446597099929</v>
+        <v>21.05237112596086</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06753983441282461</v>
+        <v>0.06744318420728668</v>
       </c>
       <c r="C28">
-        <v>257.330415008343</v>
+        <v>255.8622138929822</v>
       </c>
       <c r="D28">
-        <v>330.032415008343</v>
+        <v>331.5062138929821</v>
       </c>
       <c r="E28">
-        <v>-37.10799999999998</v>
+        <v>-34.16599999999998</v>
       </c>
       <c r="F28">
-        <v>76.492</v>
+        <v>79.434</v>
       </c>
       <c r="G28">
         <v>3.79</v>
@@ -3577,28 +3577,28 @@
         <v>81</v>
       </c>
       <c r="M28">
-        <v>3.8475476</v>
+        <v>3.9955302</v>
       </c>
       <c r="N28">
-        <v>77.1524524</v>
+        <v>77.0044698</v>
       </c>
       <c r="O28">
-        <v>14.658965956</v>
+        <v>14.630849262</v>
       </c>
       <c r="P28">
-        <v>62.493486444</v>
+        <v>62.373620538</v>
       </c>
       <c r="Q28">
-        <v>117.993486444</v>
+        <v>117.873620538</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07695493839570894</v>
+        <v>0.07731859480450229</v>
       </c>
       <c r="T28">
-        <v>0.5706136378798484</v>
+        <v>0.5772741327177543</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>21.05237112596086</v>
+        <v>20.2726536768512</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06744318420728668</v>
+        <v>0.06734653400174873</v>
       </c>
       <c r="C29">
-        <v>255.8622138929822</v>
+        <v>254.4072346689113</v>
       </c>
       <c r="D29">
-        <v>331.5062138929821</v>
+        <v>332.9932346689113</v>
       </c>
       <c r="E29">
-        <v>-34.16599999999998</v>
+        <v>-31.22399999999998</v>
       </c>
       <c r="F29">
-        <v>79.434</v>
+        <v>82.376</v>
       </c>
       <c r="G29">
         <v>3.79</v>
@@ -3659,28 +3659,28 @@
         <v>81</v>
       </c>
       <c r="M29">
-        <v>3.9955302</v>
+        <v>4.1435128</v>
       </c>
       <c r="N29">
-        <v>77.0044698</v>
+        <v>76.8564872</v>
       </c>
       <c r="O29">
-        <v>14.630849262</v>
+        <v>14.602732568</v>
       </c>
       <c r="P29">
-        <v>62.373620538</v>
+        <v>62.253754632</v>
       </c>
       <c r="Q29">
-        <v>117.873620538</v>
+        <v>117.753754632</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07731859480450229</v>
+        <v>0.07769235278020657</v>
       </c>
       <c r="T29">
-        <v>0.5772741327177543</v>
+        <v>0.5841196413011577</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>20.2726536768512</v>
+        <v>19.54863033124937</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06734653400174873</v>
+        <v>0.0672498837962108</v>
       </c>
       <c r="C30">
-        <v>254.4072346689113</v>
+        <v>252.9656560641626</v>
       </c>
       <c r="D30">
-        <v>332.9932346689113</v>
+        <v>334.4936560641626</v>
       </c>
       <c r="E30">
-        <v>-31.22399999999998</v>
+        <v>-28.28199999999997</v>
       </c>
       <c r="F30">
-        <v>82.376</v>
+        <v>85.31800000000001</v>
       </c>
       <c r="G30">
         <v>3.79</v>
@@ -3741,28 +3741,28 @@
         <v>81</v>
       </c>
       <c r="M30">
-        <v>4.1435128</v>
+        <v>4.291495400000001</v>
       </c>
       <c r="N30">
-        <v>76.8564872</v>
+        <v>76.7085046</v>
       </c>
       <c r="O30">
-        <v>14.602732568</v>
+        <v>14.574615874</v>
       </c>
       <c r="P30">
-        <v>62.253754632</v>
+        <v>62.133888726</v>
       </c>
       <c r="Q30">
-        <v>117.753754632</v>
+        <v>117.633888726</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07769235278020657</v>
+        <v>0.07807663914959267</v>
       </c>
       <c r="T30">
-        <v>0.5841196413011577</v>
+        <v>0.5911579811122626</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>19.54863033124937</v>
+        <v>18.8745396301718</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06724988379621079</v>
+        <v>0.06715323359067285</v>
       </c>
       <c r="C31">
-        <v>252.9656560641629</v>
+        <v>251.537660042645</v>
       </c>
       <c r="D31">
-        <v>334.4936560641628</v>
+        <v>336.007660042645</v>
       </c>
       <c r="E31">
-        <v>-28.28199999999998</v>
+        <v>-25.33999999999999</v>
       </c>
       <c r="F31">
-        <v>85.318</v>
+        <v>88.25999999999999</v>
       </c>
       <c r="G31">
         <v>3.79</v>
@@ -3823,28 +3823,28 @@
         <v>81</v>
       </c>
       <c r="M31">
-        <v>4.2914954</v>
+        <v>4.439477999999999</v>
       </c>
       <c r="N31">
-        <v>76.7085046</v>
+        <v>76.56052200000001</v>
       </c>
       <c r="O31">
-        <v>14.574615874</v>
+        <v>14.54649918</v>
       </c>
       <c r="P31">
-        <v>62.133888726</v>
+        <v>62.01402282000001</v>
       </c>
       <c r="Q31">
-        <v>117.633888726</v>
+        <v>117.51402282</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07807663914959266</v>
+        <v>0.07847190512953264</v>
       </c>
       <c r="T31">
-        <v>0.5911579811122625</v>
+        <v>0.5983974163465418</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>18.87453963017181</v>
+        <v>18.24538830916608</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06715323359067285</v>
+        <v>0.0670565833851349</v>
       </c>
       <c r="C32">
-        <v>251.537660042645</v>
+        <v>250.1234318777066</v>
       </c>
       <c r="D32">
-        <v>336.007660042645</v>
+        <v>337.5354318777066</v>
       </c>
       <c r="E32">
-        <v>-25.33999999999999</v>
+        <v>-22.39799999999998</v>
       </c>
       <c r="F32">
-        <v>88.25999999999999</v>
+        <v>91.202</v>
       </c>
       <c r="G32">
         <v>3.79</v>
@@ -3905,28 +3905,28 @@
         <v>81</v>
       </c>
       <c r="M32">
-        <v>4.439477999999999</v>
+        <v>4.5874606</v>
       </c>
       <c r="N32">
-        <v>76.56052200000001</v>
+        <v>76.4125394</v>
       </c>
       <c r="O32">
-        <v>14.54649918</v>
+        <v>14.518382486</v>
       </c>
       <c r="P32">
-        <v>62.01402282000001</v>
+        <v>61.894156914</v>
       </c>
       <c r="Q32">
-        <v>117.51402282</v>
+        <v>117.394156914</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07847190512953264</v>
+        <v>0.07887862809439841</v>
       </c>
       <c r="T32">
-        <v>0.5983974163465418</v>
+        <v>0.6058466902832639</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>18.24538830916608</v>
+        <v>17.65682739596717</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0670565833851349</v>
+        <v>0.06695993317959696</v>
       </c>
       <c r="C33">
-        <v>250.1234318777066</v>
+        <v>248.7231602277174</v>
       </c>
       <c r="D33">
-        <v>337.5354318777066</v>
+        <v>339.0771602277173</v>
       </c>
       <c r="E33">
-        <v>-22.39799999999998</v>
+        <v>-19.45599999999999</v>
       </c>
       <c r="F33">
-        <v>91.202</v>
+        <v>94.14399999999999</v>
       </c>
       <c r="G33">
         <v>3.79</v>
@@ -3987,28 +3987,28 @@
         <v>81</v>
       </c>
       <c r="M33">
-        <v>4.5874606</v>
+        <v>4.7354432</v>
       </c>
       <c r="N33">
-        <v>76.4125394</v>
+        <v>76.26455679999999</v>
       </c>
       <c r="O33">
-        <v>14.518382486</v>
+        <v>14.490265792</v>
       </c>
       <c r="P33">
-        <v>61.894156914</v>
+        <v>61.77429100799999</v>
       </c>
       <c r="Q33">
-        <v>117.394156914</v>
+        <v>117.274291008</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07887862809439841</v>
+        <v>0.0792973134994073</v>
       </c>
       <c r="T33">
-        <v>0.6058466902832639</v>
+        <v>0.6135150605122426</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>17.65682739596717</v>
+        <v>17.1050515398432</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06695993317959696</v>
+        <v>0.06686328297405902</v>
       </c>
       <c r="C34">
-        <v>248.7231602277174</v>
+        <v>247.3370372137309</v>
       </c>
       <c r="D34">
-        <v>339.0771602277173</v>
+        <v>340.6330372137309</v>
       </c>
       <c r="E34">
-        <v>-19.45599999999999</v>
+        <v>-16.51399999999998</v>
       </c>
       <c r="F34">
-        <v>94.14399999999999</v>
+        <v>97.086</v>
       </c>
       <c r="G34">
         <v>3.79</v>
@@ -4069,28 +4069,28 @@
         <v>81</v>
       </c>
       <c r="M34">
-        <v>4.7354432</v>
+        <v>4.883425799999999</v>
       </c>
       <c r="N34">
-        <v>76.26455679999999</v>
+        <v>76.1165742</v>
       </c>
       <c r="O34">
-        <v>14.490265792</v>
+        <v>14.462149098</v>
       </c>
       <c r="P34">
-        <v>61.77429100799999</v>
+        <v>61.654425102</v>
       </c>
       <c r="Q34">
-        <v>117.274291008</v>
+        <v>117.154425102</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0792973134994073</v>
+        <v>0.07972849697620751</v>
       </c>
       <c r="T34">
-        <v>0.6135150605122426</v>
+        <v>0.6214123373152206</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>17.1050515398432</v>
+        <v>16.58671664469644</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06686328297405902</v>
+        <v>0.06676663276852107</v>
       </c>
       <c r="C35">
-        <v>247.3370372137309</v>
+        <v>245.9652584992943</v>
       </c>
       <c r="D35">
-        <v>340.6330372137309</v>
+        <v>342.2032584992943</v>
       </c>
       <c r="E35">
-        <v>-16.51399999999998</v>
+        <v>-13.57199999999997</v>
       </c>
       <c r="F35">
-        <v>97.086</v>
+        <v>100.028</v>
       </c>
       <c r="G35">
         <v>3.79</v>
@@ -4151,28 +4151,28 @@
         <v>81</v>
       </c>
       <c r="M35">
-        <v>4.883425799999999</v>
+        <v>5.0314084</v>
       </c>
       <c r="N35">
-        <v>76.1165742</v>
+        <v>75.9685916</v>
       </c>
       <c r="O35">
-        <v>14.462149098</v>
+        <v>14.434032404</v>
       </c>
       <c r="P35">
-        <v>61.654425102</v>
+        <v>61.534559196</v>
       </c>
       <c r="Q35">
-        <v>117.154425102</v>
+        <v>117.034559196</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07972849697620751</v>
+        <v>0.08017274661897134</v>
       </c>
       <c r="T35">
-        <v>0.6214123373152206</v>
+        <v>0.6295489255364707</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>16.58671664469644</v>
+        <v>16.09887203749948</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06676663276852107</v>
+        <v>0.06666998256298313</v>
       </c>
       <c r="C36">
-        <v>245.9652584992943</v>
+        <v>244.608023372475</v>
       </c>
       <c r="D36">
-        <v>342.2032584992943</v>
+        <v>343.788023372475</v>
       </c>
       <c r="E36">
-        <v>-13.57199999999997</v>
+        <v>-10.62999999999998</v>
       </c>
       <c r="F36">
-        <v>100.028</v>
+        <v>102.97</v>
       </c>
       <c r="G36">
         <v>3.79</v>
@@ -4233,28 +4233,28 @@
         <v>81</v>
       </c>
       <c r="M36">
-        <v>5.0314084</v>
+        <v>5.179391</v>
       </c>
       <c r="N36">
-        <v>75.9685916</v>
+        <v>75.820609</v>
       </c>
       <c r="O36">
-        <v>14.434032404</v>
+        <v>14.40591571</v>
       </c>
       <c r="P36">
-        <v>61.534559196</v>
+        <v>61.41469329</v>
       </c>
       <c r="Q36">
-        <v>117.034559196</v>
+        <v>116.91469329</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08017274661897134</v>
+        <v>0.08063066548151253</v>
       </c>
       <c r="T36">
-        <v>0.6295489255364707</v>
+        <v>0.6379358703183745</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>16.09887203749948</v>
+        <v>15.6389042649995</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06666998256298313</v>
+        <v>0.06657333235744521</v>
       </c>
       <c r="C37">
-        <v>244.608023372475</v>
+        <v>243.265534830179</v>
       </c>
       <c r="D37">
-        <v>343.788023372475</v>
+        <v>345.3875348301789</v>
       </c>
       <c r="E37">
-        <v>-10.62999999999998</v>
+        <v>-7.687999999999974</v>
       </c>
       <c r="F37">
-        <v>102.97</v>
+        <v>105.912</v>
       </c>
       <c r="G37">
         <v>3.79</v>
@@ -4315,28 +4315,28 @@
         <v>81</v>
       </c>
       <c r="M37">
-        <v>5.179391</v>
+        <v>5.3273736</v>
       </c>
       <c r="N37">
-        <v>75.820609</v>
+        <v>75.6726264</v>
       </c>
       <c r="O37">
-        <v>14.40591571</v>
+        <v>14.377799016</v>
       </c>
       <c r="P37">
-        <v>61.41469329</v>
+        <v>61.294827384</v>
       </c>
       <c r="Q37">
-        <v>116.91469329</v>
+        <v>116.794827384</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08063066548151253</v>
+        <v>0.08110289430850814</v>
       </c>
       <c r="T37">
-        <v>0.6379358703183745</v>
+        <v>0.6465849071247131</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>15.6389042649995</v>
+        <v>15.2044902576384</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06657333235744521</v>
+        <v>0.06647668215190726</v>
       </c>
       <c r="C38">
-        <v>243.265534830179</v>
+        <v>241.9379996648335</v>
       </c>
       <c r="D38">
-        <v>345.3875348301789</v>
+        <v>347.0019996648335</v>
       </c>
       <c r="E38">
-        <v>-7.687999999999988</v>
+        <v>-4.745999999999981</v>
       </c>
       <c r="F38">
-        <v>105.912</v>
+        <v>108.854</v>
       </c>
       <c r="G38">
         <v>3.79</v>
@@ -4397,28 +4397,28 @@
         <v>81</v>
       </c>
       <c r="M38">
-        <v>5.3273736</v>
+        <v>5.475356199999999</v>
       </c>
       <c r="N38">
-        <v>75.6726264</v>
+        <v>75.52464380000001</v>
       </c>
       <c r="O38">
-        <v>14.377799016</v>
+        <v>14.349682322</v>
       </c>
       <c r="P38">
-        <v>61.294827384</v>
+        <v>61.17496147800001</v>
       </c>
       <c r="Q38">
-        <v>116.794827384</v>
+        <v>116.674961478</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08110289430850813</v>
+        <v>0.08159011452683693</v>
       </c>
       <c r="T38">
-        <v>0.6465849071247129</v>
+        <v>0.6555085165280781</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>15.2044902576384</v>
+        <v>14.79355808851304</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06647668215190726</v>
+        <v>0.06638003194636934</v>
       </c>
       <c r="C39">
-        <v>241.9379996648335</v>
+        <v>240.6256285535094</v>
       </c>
       <c r="D39">
-        <v>347.0019996648335</v>
+        <v>348.6316285535094</v>
       </c>
       <c r="E39">
-        <v>-4.745999999999981</v>
+        <v>-1.803999999999988</v>
       </c>
       <c r="F39">
-        <v>108.854</v>
+        <v>111.796</v>
       </c>
       <c r="G39">
         <v>3.79</v>
@@ -4479,28 +4479,28 @@
         <v>81</v>
       </c>
       <c r="M39">
-        <v>5.475356199999999</v>
+        <v>5.623338799999999</v>
       </c>
       <c r="N39">
-        <v>75.52464380000001</v>
+        <v>75.3766612</v>
       </c>
       <c r="O39">
-        <v>14.349682322</v>
+        <v>14.321565628</v>
       </c>
       <c r="P39">
-        <v>61.17496147800001</v>
+        <v>61.055095572</v>
       </c>
       <c r="Q39">
-        <v>116.674961478</v>
+        <v>116.555095572</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08159011452683693</v>
+        <v>0.08209305152640214</v>
       </c>
       <c r="T39">
-        <v>0.6555085165280781</v>
+        <v>0.6647199842992937</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>14.79355808851304</v>
+        <v>14.40425392828901</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06638003194636934</v>
+        <v>0.06628338174083138</v>
       </c>
       <c r="C40">
-        <v>240.6256285535094</v>
+        <v>239.3286361495725</v>
       </c>
       <c r="D40">
-        <v>348.6316285535094</v>
+        <v>350.2766361495725</v>
       </c>
       <c r="E40">
-        <v>-1.803999999999988</v>
+        <v>1.138000000000019</v>
       </c>
       <c r="F40">
-        <v>111.796</v>
+        <v>114.738</v>
       </c>
       <c r="G40">
         <v>3.79</v>
@@ -4561,28 +4561,28 @@
         <v>81</v>
       </c>
       <c r="M40">
-        <v>5.623338799999999</v>
+        <v>5.7713214</v>
       </c>
       <c r="N40">
-        <v>75.3766612</v>
+        <v>75.22867859999999</v>
       </c>
       <c r="O40">
-        <v>14.321565628</v>
+        <v>14.293448934</v>
       </c>
       <c r="P40">
-        <v>61.055095572</v>
+        <v>60.935229666</v>
       </c>
       <c r="Q40">
-        <v>116.555095572</v>
+        <v>116.435229666</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08209305152640214</v>
+        <v>0.082612478263658</v>
       </c>
       <c r="T40">
-        <v>0.6647199842992937</v>
+        <v>0.6742334674072703</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>14.40425392828901</v>
+        <v>14.03491408397391</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06628338174083138</v>
+        <v>0.06618673153529345</v>
       </c>
       <c r="C41">
-        <v>239.3286361495725</v>
+        <v>238.0472411769348</v>
       </c>
       <c r="D41">
-        <v>350.2766361495725</v>
+        <v>351.9372411769348</v>
       </c>
       <c r="E41">
-        <v>1.138000000000019</v>
+        <v>4.080000000000027</v>
       </c>
       <c r="F41">
-        <v>114.738</v>
+        <v>117.68</v>
       </c>
       <c r="G41">
         <v>3.79</v>
@@ -4643,28 +4643,28 @@
         <v>81</v>
       </c>
       <c r="M41">
-        <v>5.7713214</v>
+        <v>5.919304</v>
       </c>
       <c r="N41">
-        <v>75.22867859999999</v>
+        <v>75.080696</v>
       </c>
       <c r="O41">
-        <v>14.293448934</v>
+        <v>14.26533224</v>
       </c>
       <c r="P41">
-        <v>60.935229666</v>
+        <v>60.81536376</v>
       </c>
       <c r="Q41">
-        <v>116.435229666</v>
+        <v>116.31536376</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.082612478263658</v>
+        <v>0.08314921922548907</v>
       </c>
       <c r="T41">
-        <v>0.6742334674072703</v>
+        <v>0.6840640666188462</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>14.03491408397391</v>
+        <v>13.68404123187456</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06618673153529345</v>
+        <v>0.0660900813297555</v>
       </c>
       <c r="C42">
-        <v>238.0472411769348</v>
+        <v>236.7816665270061</v>
       </c>
       <c r="D42">
-        <v>351.9372411769348</v>
+        <v>353.613666527006</v>
       </c>
       <c r="E42">
-        <v>4.080000000000027</v>
+        <v>7.02200000000002</v>
       </c>
       <c r="F42">
-        <v>117.68</v>
+        <v>120.622</v>
       </c>
       <c r="G42">
         <v>3.79</v>
@@ -4725,28 +4725,28 @@
         <v>81</v>
       </c>
       <c r="M42">
-        <v>5.919304</v>
+        <v>6.0672866</v>
       </c>
       <c r="N42">
-        <v>75.080696</v>
+        <v>74.9327134</v>
       </c>
       <c r="O42">
-        <v>14.26533224</v>
+        <v>14.237215546</v>
       </c>
       <c r="P42">
-        <v>60.81536376</v>
+        <v>60.695497854</v>
       </c>
       <c r="Q42">
-        <v>116.31536376</v>
+        <v>116.195497854</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08314921922548907</v>
+        <v>0.08370415479619575</v>
       </c>
       <c r="T42">
-        <v>0.6840640666188462</v>
+        <v>0.694227906481662</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>13.68404123187456</v>
+        <v>13.3502841286581</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0660900813297555</v>
+        <v>0.06599343112421756</v>
       </c>
       <c r="C43">
-        <v>236.7816665270061</v>
+        <v>235.5321393584246</v>
       </c>
       <c r="D43">
-        <v>353.613666527006</v>
+        <v>355.3061393584246</v>
       </c>
       <c r="E43">
-        <v>7.02200000000002</v>
+        <v>9.964000000000027</v>
       </c>
       <c r="F43">
-        <v>120.622</v>
+        <v>123.564</v>
       </c>
       <c r="G43">
         <v>3.79</v>
@@ -4807,28 +4807,28 @@
         <v>81</v>
       </c>
       <c r="M43">
-        <v>6.0672866</v>
+        <v>6.2152692</v>
       </c>
       <c r="N43">
-        <v>74.9327134</v>
+        <v>74.78473080000001</v>
       </c>
       <c r="O43">
-        <v>14.237215546</v>
+        <v>14.209098852</v>
       </c>
       <c r="P43">
-        <v>60.695497854</v>
+        <v>60.57563194800001</v>
       </c>
       <c r="Q43">
-        <v>116.195497854</v>
+        <v>116.075631948</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08370415479619575</v>
+        <v>0.08427822607623717</v>
       </c>
       <c r="T43">
-        <v>0.694227906481662</v>
+        <v>0.7047422235811267</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>13.3502841286581</v>
+        <v>13.03242022083291</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06599343112421756</v>
+        <v>0.06641923091867963</v>
       </c>
       <c r="C44">
-        <v>235.5321393584246</v>
+        <v>225.2528491507248</v>
       </c>
       <c r="D44">
-        <v>355.3061393584246</v>
+        <v>347.9688491507247</v>
       </c>
       <c r="E44">
-        <v>9.964000000000013</v>
+        <v>12.90600000000002</v>
       </c>
       <c r="F44">
-        <v>123.564</v>
+        <v>126.506</v>
       </c>
       <c r="G44">
         <v>3.79</v>
@@ -4889,45 +4889,45 @@
         <v>81</v>
       </c>
       <c r="M44">
-        <v>6.215269199999999</v>
+        <v>6.5530108</v>
       </c>
       <c r="N44">
-        <v>74.78473080000001</v>
+        <v>74.4469892</v>
       </c>
       <c r="O44">
-        <v>14.209098852</v>
+        <v>14.144927948</v>
       </c>
       <c r="P44">
-        <v>60.57563194800001</v>
+        <v>60.302061252</v>
       </c>
       <c r="Q44">
-        <v>116.075631948</v>
+        <v>115.802061252</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08427822607623717</v>
+        <v>0.08487244020820986</v>
       </c>
       <c r="T44">
-        <v>0.7047422235811266</v>
+        <v>0.71562546408759</v>
       </c>
       <c r="U44">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V44">
         <v>0.19</v>
       </c>
       <c r="W44">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y44">
-        <v>13.03242022083291</v>
+        <v>12.36073042943863</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06641923091867963</v>
+        <v>0.06633473071314169</v>
       </c>
       <c r="C45">
-        <v>225.2528491507248</v>
+        <v>223.7427373836305</v>
       </c>
       <c r="D45">
-        <v>347.9688491507247</v>
+        <v>349.4007373836305</v>
       </c>
       <c r="E45">
-        <v>12.90600000000002</v>
+        <v>15.84800000000003</v>
       </c>
       <c r="F45">
-        <v>126.506</v>
+        <v>129.448</v>
       </c>
       <c r="G45">
         <v>3.79</v>
@@ -4971,28 +4971,28 @@
         <v>81</v>
       </c>
       <c r="M45">
-        <v>6.5530108</v>
+        <v>6.7054064</v>
       </c>
       <c r="N45">
-        <v>74.4469892</v>
+        <v>74.2945936</v>
       </c>
       <c r="O45">
-        <v>14.144927948</v>
+        <v>14.115972784</v>
       </c>
       <c r="P45">
-        <v>60.302061252</v>
+        <v>60.178620816</v>
       </c>
       <c r="Q45">
-        <v>115.802061252</v>
+        <v>115.678620816</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08487244020820986</v>
+        <v>0.08548787627346728</v>
       </c>
       <c r="T45">
-        <v>0.71562546408759</v>
+        <v>0.7268973917549986</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>12.36073042943863</v>
+        <v>12.07980473786048</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06633473071314169</v>
+        <v>0.06625023050760374</v>
       </c>
       <c r="C46">
-        <v>223.7427373836305</v>
+        <v>222.2444587203191</v>
       </c>
       <c r="D46">
-        <v>349.4007373836305</v>
+        <v>350.8444587203191</v>
       </c>
       <c r="E46">
-        <v>15.84800000000003</v>
+        <v>18.79000000000001</v>
       </c>
       <c r="F46">
-        <v>129.448</v>
+        <v>132.39</v>
       </c>
       <c r="G46">
         <v>3.79</v>
@@ -5053,28 +5053,28 @@
         <v>81</v>
       </c>
       <c r="M46">
-        <v>6.7054064</v>
+        <v>6.857802</v>
       </c>
       <c r="N46">
-        <v>74.2945936</v>
+        <v>74.14219800000001</v>
       </c>
       <c r="O46">
-        <v>14.115972784</v>
+        <v>14.08701762</v>
       </c>
       <c r="P46">
-        <v>60.178620816</v>
+        <v>60.05518038000001</v>
       </c>
       <c r="Q46">
-        <v>115.678620816</v>
+        <v>115.55518038</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08548787627346728</v>
+        <v>0.08612569183200679</v>
       </c>
       <c r="T46">
-        <v>0.7268973917549986</v>
+        <v>0.7385792077012218</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>12.07980473786048</v>
+        <v>11.8113646325747</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06625023050760374</v>
+        <v>0.06616573030206579</v>
       </c>
       <c r="C47">
-        <v>222.2444587203191</v>
+        <v>220.7581604522973</v>
       </c>
       <c r="D47">
-        <v>350.8444587203191</v>
+        <v>352.3001604522972</v>
       </c>
       <c r="E47">
-        <v>18.79000000000001</v>
+        <v>21.73200000000001</v>
       </c>
       <c r="F47">
-        <v>132.39</v>
+        <v>135.332</v>
       </c>
       <c r="G47">
         <v>3.79</v>
@@ -5135,28 +5135,28 @@
         <v>81</v>
       </c>
       <c r="M47">
-        <v>6.857802</v>
+        <v>7.0101976</v>
       </c>
       <c r="N47">
-        <v>74.14219800000001</v>
+        <v>73.9898024</v>
       </c>
       <c r="O47">
-        <v>14.08701762</v>
+        <v>14.058062456</v>
       </c>
       <c r="P47">
-        <v>60.05518038000001</v>
+        <v>59.931739944</v>
       </c>
       <c r="Q47">
-        <v>115.55518038</v>
+        <v>115.431739944</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08612569183200679</v>
+        <v>0.08678713018901073</v>
       </c>
       <c r="T47">
-        <v>0.7385792077012218</v>
+        <v>0.7506936834973053</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>11.8113646325747</v>
+        <v>11.55459583621438</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06616573030206579</v>
+        <v>0.06608123009652786</v>
       </c>
       <c r="C48">
-        <v>220.7581604522973</v>
+        <v>219.2839923257872</v>
       </c>
       <c r="D48">
-        <v>352.3001604522972</v>
+        <v>353.7679923257871</v>
       </c>
       <c r="E48">
-        <v>21.73200000000001</v>
+        <v>24.67400000000002</v>
       </c>
       <c r="F48">
-        <v>135.332</v>
+        <v>138.274</v>
       </c>
       <c r="G48">
         <v>3.79</v>
@@ -5217,28 +5217,28 @@
         <v>81</v>
       </c>
       <c r="M48">
-        <v>7.0101976</v>
+        <v>7.1625932</v>
       </c>
       <c r="N48">
-        <v>73.9898024</v>
+        <v>73.8374068</v>
       </c>
       <c r="O48">
-        <v>14.058062456</v>
+        <v>14.029107292</v>
       </c>
       <c r="P48">
-        <v>59.931739944</v>
+        <v>59.808299508</v>
       </c>
       <c r="Q48">
-        <v>115.431739944</v>
+        <v>115.308299508</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08678713018901073</v>
+        <v>0.08747352848401482</v>
       </c>
       <c r="T48">
-        <v>0.7506936834973053</v>
+        <v>0.7632653093234296</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>11.55459583621438</v>
+        <v>11.30875337161407</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06608123009652786</v>
+        <v>0.06599672989098992</v>
       </c>
       <c r="C49">
-        <v>219.2839923257872</v>
+        <v>217.8221065930779</v>
       </c>
       <c r="D49">
-        <v>353.7679923257871</v>
+        <v>355.2481065930779</v>
       </c>
       <c r="E49">
-        <v>24.67400000000002</v>
+        <v>27.61600000000003</v>
       </c>
       <c r="F49">
-        <v>138.274</v>
+        <v>141.216</v>
       </c>
       <c r="G49">
         <v>3.79</v>
@@ -5299,28 +5299,28 @@
         <v>81</v>
       </c>
       <c r="M49">
-        <v>7.1625932</v>
+        <v>7.3149888</v>
       </c>
       <c r="N49">
-        <v>73.8374068</v>
+        <v>73.68501120000001</v>
       </c>
       <c r="O49">
-        <v>14.029107292</v>
+        <v>14.000152128</v>
       </c>
       <c r="P49">
-        <v>59.808299508</v>
+        <v>59.684859072</v>
       </c>
       <c r="Q49">
-        <v>115.308299508</v>
+        <v>115.184859072</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08747352848401482</v>
+        <v>0.08818632671344215</v>
       </c>
       <c r="T49">
-        <v>0.7632653093234296</v>
+        <v>0.7763204592197896</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>11.30875337161407</v>
+        <v>11.07315434303878</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06599672989098992</v>
+        <v>0.06591222968545196</v>
       </c>
       <c r="C50">
-        <v>217.822106593078</v>
+        <v>216.3726580651706</v>
       </c>
       <c r="D50">
-        <v>355.2481065930779</v>
+        <v>356.7406580651705</v>
       </c>
       <c r="E50">
-        <v>27.616</v>
+        <v>30.55800000000001</v>
       </c>
       <c r="F50">
-        <v>141.216</v>
+        <v>144.158</v>
       </c>
       <c r="G50">
         <v>3.79</v>
@@ -5381,28 +5381,28 @@
         <v>81</v>
       </c>
       <c r="M50">
-        <v>7.314988799999999</v>
+        <v>7.467384399999999</v>
       </c>
       <c r="N50">
-        <v>73.68501120000001</v>
+        <v>73.5326156</v>
       </c>
       <c r="O50">
-        <v>14.000152128</v>
+        <v>13.971196964</v>
       </c>
       <c r="P50">
-        <v>59.684859072</v>
+        <v>59.561418636</v>
       </c>
       <c r="Q50">
-        <v>115.184859072</v>
+        <v>115.061418636</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08818632671344215</v>
+        <v>0.0889270778146117</v>
       </c>
       <c r="T50">
-        <v>0.7763204592197895</v>
+        <v>0.7898875757787518</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>11.07315434303878</v>
+        <v>10.84717160134411</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06591222968545196</v>
+        <v>0.06582772947991403</v>
       </c>
       <c r="C51">
-        <v>216.3726580651706</v>
+        <v>214.9358041657547</v>
       </c>
       <c r="D51">
-        <v>356.7406580651705</v>
+        <v>358.2458041657546</v>
       </c>
       <c r="E51">
-        <v>30.55800000000001</v>
+        <v>33.50000000000001</v>
       </c>
       <c r="F51">
-        <v>144.158</v>
+        <v>147.1</v>
       </c>
       <c r="G51">
         <v>3.79</v>
@@ -5463,28 +5463,28 @@
         <v>81</v>
       </c>
       <c r="M51">
-        <v>7.467384399999999</v>
+        <v>7.61978</v>
       </c>
       <c r="N51">
-        <v>73.5326156</v>
+        <v>73.38021999999999</v>
       </c>
       <c r="O51">
-        <v>13.971196964</v>
+        <v>13.9422418</v>
       </c>
       <c r="P51">
-        <v>59.561418636</v>
+        <v>59.4379782</v>
       </c>
       <c r="Q51">
-        <v>115.061418636</v>
+        <v>114.9379782</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.0889270778146117</v>
+        <v>0.08969745895982806</v>
       </c>
       <c r="T51">
-        <v>0.7898875757787518</v>
+        <v>0.8039973770000726</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>10.84717160134411</v>
+        <v>10.63022816931722</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06582772947991403</v>
+        <v>0.06574322927437609</v>
       </c>
       <c r="C52">
-        <v>214.9358041657547</v>
+        <v>213.5117049865612</v>
       </c>
       <c r="D52">
-        <v>358.2458041657546</v>
+        <v>359.7637049865612</v>
       </c>
       <c r="E52">
-        <v>33.50000000000001</v>
+        <v>36.44200000000002</v>
       </c>
       <c r="F52">
-        <v>147.1</v>
+        <v>150.042</v>
       </c>
       <c r="G52">
         <v>3.79</v>
@@ -5545,28 +5545,28 @@
         <v>81</v>
       </c>
       <c r="M52">
-        <v>7.61978</v>
+        <v>7.7721756</v>
       </c>
       <c r="N52">
-        <v>73.38021999999999</v>
+        <v>73.2278244</v>
       </c>
       <c r="O52">
-        <v>13.9422418</v>
+        <v>13.913286636</v>
       </c>
       <c r="P52">
-        <v>59.4379782</v>
+        <v>59.314537764</v>
       </c>
       <c r="Q52">
-        <v>114.9379782</v>
+        <v>114.814537764</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08969745895982806</v>
+        <v>0.0904992842334206</v>
       </c>
       <c r="T52">
-        <v>0.8039973770000726</v>
+        <v>0.8186830884753248</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>10.63022816931722</v>
+        <v>10.42179232286002</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06574322927437609</v>
+        <v>0.06565872906883816</v>
       </c>
       <c r="C53">
-        <v>213.5117049865612</v>
+        <v>212.1005233441245</v>
       </c>
       <c r="D53">
-        <v>359.7637049865612</v>
+        <v>361.2945233441245</v>
       </c>
       <c r="E53">
-        <v>36.44200000000002</v>
+        <v>39.38400000000003</v>
       </c>
       <c r="F53">
-        <v>150.042</v>
+        <v>152.984</v>
       </c>
       <c r="G53">
         <v>3.79</v>
@@ -5627,28 +5627,28 @@
         <v>81</v>
       </c>
       <c r="M53">
-        <v>7.7721756</v>
+        <v>7.9245712</v>
       </c>
       <c r="N53">
-        <v>73.2278244</v>
+        <v>73.0754288</v>
       </c>
       <c r="O53">
-        <v>13.913286636</v>
+        <v>13.884331472</v>
       </c>
       <c r="P53">
-        <v>59.314537764</v>
+        <v>59.191097328</v>
       </c>
       <c r="Q53">
-        <v>114.814537764</v>
+        <v>114.691097328</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0904992842334206</v>
+        <v>0.09133451889341281</v>
       </c>
       <c r="T53">
-        <v>0.8186830884753248</v>
+        <v>0.8339807045953791</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>10.42179232286002</v>
+        <v>10.2213732397281</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06565872906883816</v>
+        <v>0.06557422886330021</v>
       </c>
       <c r="C54">
-        <v>212.1005233441245</v>
+        <v>210.7024248380015</v>
       </c>
       <c r="D54">
-        <v>361.2945233441245</v>
+        <v>362.8384248380015</v>
       </c>
       <c r="E54">
-        <v>39.38400000000003</v>
+        <v>42.32600000000001</v>
       </c>
       <c r="F54">
-        <v>152.984</v>
+        <v>155.926</v>
       </c>
       <c r="G54">
         <v>3.79</v>
@@ -5709,28 +5709,28 @@
         <v>81</v>
       </c>
       <c r="M54">
-        <v>7.9245712</v>
+        <v>8.076966799999999</v>
       </c>
       <c r="N54">
-        <v>73.0754288</v>
+        <v>72.92303320000001</v>
       </c>
       <c r="O54">
-        <v>13.884331472</v>
+        <v>13.855376308</v>
       </c>
       <c r="P54">
-        <v>59.191097328</v>
+        <v>59.067656892</v>
       </c>
       <c r="Q54">
-        <v>114.691097328</v>
+        <v>114.567656892</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09133451889341281</v>
+        <v>0.09220529545383023</v>
       </c>
       <c r="T54">
-        <v>0.8339807045953791</v>
+        <v>0.849929283103521</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>10.2213732397281</v>
+        <v>10.02851714086531</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06557422886330021</v>
+        <v>0.06548972865776226</v>
       </c>
       <c r="C55">
-        <v>210.7024248380015</v>
+        <v>209.3175779104889</v>
       </c>
       <c r="D55">
-        <v>362.8384248380015</v>
+        <v>364.3955779104888</v>
       </c>
       <c r="E55">
-        <v>42.32600000000001</v>
+        <v>45.26800000000001</v>
       </c>
       <c r="F55">
-        <v>155.926</v>
+        <v>158.868</v>
       </c>
       <c r="G55">
         <v>3.79</v>
@@ -5791,28 +5791,28 @@
         <v>81</v>
       </c>
       <c r="M55">
-        <v>8.076966799999999</v>
+        <v>8.229362399999999</v>
       </c>
       <c r="N55">
-        <v>72.92303320000001</v>
+        <v>72.7706376</v>
       </c>
       <c r="O55">
-        <v>13.855376308</v>
+        <v>13.826421144</v>
       </c>
       <c r="P55">
-        <v>59.067656892</v>
+        <v>58.944216456</v>
       </c>
       <c r="Q55">
-        <v>114.567656892</v>
+        <v>114.444216456</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09220529545383023</v>
+        <v>0.09311393186470057</v>
       </c>
       <c r="T55">
-        <v>0.849929283103521</v>
+        <v>0.8665712780685385</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>10.02851714086531</v>
+        <v>9.842803860478913</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06548972865776226</v>
+        <v>0.06616257845222433</v>
       </c>
       <c r="C56">
-        <v>209.3175779104889</v>
+        <v>194.3346917194192</v>
       </c>
       <c r="D56">
-        <v>364.3955779104888</v>
+        <v>352.3546917194192</v>
       </c>
       <c r="E56">
-        <v>45.26800000000001</v>
+        <v>48.21000000000002</v>
       </c>
       <c r="F56">
-        <v>158.868</v>
+        <v>161.81</v>
       </c>
       <c r="G56">
         <v>3.79</v>
@@ -5873,45 +5873,45 @@
         <v>81</v>
       </c>
       <c r="M56">
-        <v>8.229362399999999</v>
+        <v>8.656834999999999</v>
       </c>
       <c r="N56">
-        <v>72.7706376</v>
+        <v>72.343165</v>
       </c>
       <c r="O56">
-        <v>13.826421144</v>
+        <v>13.74520135</v>
       </c>
       <c r="P56">
-        <v>58.944216456</v>
+        <v>58.59796365</v>
       </c>
       <c r="Q56">
-        <v>114.444216456</v>
+        <v>114.09796365</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09311393186470057</v>
+        <v>0.09406295211605406</v>
       </c>
       <c r="T56">
-        <v>0.8665712780685385</v>
+        <v>0.8839529172542234</v>
       </c>
       <c r="U56">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V56">
         <v>0.19</v>
       </c>
       <c r="W56">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>9.842803860478913</v>
+        <v>9.35676838012969</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06616257845222433</v>
+        <v>0.06609184824668639</v>
       </c>
       <c r="C57">
-        <v>194.3346917194192</v>
+        <v>192.6208755430214</v>
       </c>
       <c r="D57">
-        <v>352.3546917194192</v>
+        <v>353.5828755430214</v>
       </c>
       <c r="E57">
-        <v>48.21000000000002</v>
+        <v>51.15200000000003</v>
       </c>
       <c r="F57">
-        <v>161.81</v>
+        <v>164.752</v>
       </c>
       <c r="G57">
         <v>3.79</v>
@@ -5955,28 +5955,28 @@
         <v>81</v>
       </c>
       <c r="M57">
-        <v>8.656834999999999</v>
+        <v>8.814232000000001</v>
       </c>
       <c r="N57">
-        <v>72.343165</v>
+        <v>72.185768</v>
       </c>
       <c r="O57">
-        <v>13.74520135</v>
+        <v>13.71529592</v>
       </c>
       <c r="P57">
-        <v>58.59796365</v>
+        <v>58.47047207999999</v>
       </c>
       <c r="Q57">
-        <v>114.09796365</v>
+        <v>113.97047208</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09406295211605406</v>
+        <v>0.09505510965155997</v>
       </c>
       <c r="T57">
-        <v>0.8839529172542234</v>
+        <v>0.9021246309483487</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>9.35676838012969</v>
+        <v>9.189683230484516</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06609184824668639</v>
+        <v>0.06602111804114844</v>
       </c>
       <c r="C58">
-        <v>192.6208755430214</v>
+        <v>190.9156513439918</v>
       </c>
       <c r="D58">
-        <v>353.5828755430214</v>
+        <v>354.8196513439918</v>
       </c>
       <c r="E58">
-        <v>51.15200000000003</v>
+        <v>54.09400000000004</v>
       </c>
       <c r="F58">
-        <v>164.752</v>
+        <v>167.694</v>
       </c>
       <c r="G58">
         <v>3.79</v>
@@ -6037,28 +6037,28 @@
         <v>81</v>
       </c>
       <c r="M58">
-        <v>8.814232000000001</v>
+        <v>8.971629</v>
       </c>
       <c r="N58">
-        <v>72.185768</v>
+        <v>72.02837099999999</v>
       </c>
       <c r="O58">
-        <v>13.71529592</v>
+        <v>13.68539049</v>
       </c>
       <c r="P58">
-        <v>58.47047207999999</v>
+        <v>58.34298050999999</v>
       </c>
       <c r="Q58">
-        <v>113.97047208</v>
+        <v>113.84298051</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09505510965155997</v>
+        <v>0.09609341404918242</v>
       </c>
       <c r="T58">
-        <v>0.9021246309483487</v>
+        <v>0.921141540628247</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>9.189683230484516</v>
+        <v>9.028460717668997</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06602111804114844</v>
+        <v>0.0659503878356105</v>
       </c>
       <c r="C59">
-        <v>190.9156513439918</v>
+        <v>189.2191095988503</v>
       </c>
       <c r="D59">
-        <v>354.8196513439918</v>
+        <v>356.0651095988503</v>
       </c>
       <c r="E59">
-        <v>54.09400000000004</v>
+        <v>57.03600000000004</v>
       </c>
       <c r="F59">
-        <v>167.694</v>
+        <v>170.636</v>
       </c>
       <c r="G59">
         <v>3.79</v>
@@ -6119,28 +6119,28 @@
         <v>81</v>
       </c>
       <c r="M59">
-        <v>8.971629</v>
+        <v>9.129026000000001</v>
       </c>
       <c r="N59">
-        <v>72.02837099999999</v>
+        <v>71.870974</v>
       </c>
       <c r="O59">
-        <v>13.68539049</v>
+        <v>13.65548506</v>
       </c>
       <c r="P59">
-        <v>58.34298050999999</v>
+        <v>58.21548894</v>
       </c>
       <c r="Q59">
-        <v>113.84298051</v>
+        <v>113.71548894</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09609341404918242</v>
+        <v>0.09718116151335834</v>
       </c>
       <c r="T59">
-        <v>0.921141540628247</v>
+        <v>0.94106401743576</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>9.028460717668997</v>
+        <v>8.872797601847118</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06595038783561051</v>
+        <v>0.06587965763007257</v>
       </c>
       <c r="C60">
-        <v>189.2191095988501</v>
+        <v>187.5313420589244</v>
       </c>
       <c r="D60">
-        <v>356.0651095988501</v>
+        <v>357.3193420589243</v>
       </c>
       <c r="E60">
-        <v>57.03600000000002</v>
+        <v>59.97799999999999</v>
       </c>
       <c r="F60">
-        <v>170.636</v>
+        <v>173.578</v>
       </c>
       <c r="G60">
         <v>3.79</v>
@@ -6201,28 +6201,28 @@
         <v>81</v>
       </c>
       <c r="M60">
-        <v>9.129026</v>
+        <v>9.286422999999999</v>
       </c>
       <c r="N60">
-        <v>71.870974</v>
+        <v>71.713577</v>
       </c>
       <c r="O60">
-        <v>13.65548506</v>
+        <v>13.62557963</v>
       </c>
       <c r="P60">
-        <v>58.21548894</v>
+        <v>58.08799737</v>
       </c>
       <c r="Q60">
-        <v>113.71548894</v>
+        <v>113.58799737</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09718116151335833</v>
+        <v>0.09832196982944527</v>
       </c>
       <c r="T60">
-        <v>0.9410640174357596</v>
+        <v>0.9619583223802242</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.87279760184712</v>
+        <v>8.722411201815813</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06587965763007257</v>
+        <v>0.06580892742453462</v>
       </c>
       <c r="C61">
-        <v>187.5313420589244</v>
+        <v>185.8524417728812</v>
       </c>
       <c r="D61">
-        <v>357.3193420589243</v>
+        <v>358.5824417728812</v>
       </c>
       <c r="E61">
-        <v>59.97799999999999</v>
+        <v>62.92</v>
       </c>
       <c r="F61">
-        <v>173.578</v>
+        <v>176.52</v>
       </c>
       <c r="G61">
         <v>3.79</v>
@@ -6283,28 +6283,28 @@
         <v>81</v>
       </c>
       <c r="M61">
-        <v>9.286422999999999</v>
+        <v>9.443819999999999</v>
       </c>
       <c r="N61">
-        <v>71.713577</v>
+        <v>71.55618</v>
       </c>
       <c r="O61">
-        <v>13.62557963</v>
+        <v>13.5956742</v>
       </c>
       <c r="P61">
-        <v>58.08799737</v>
+        <v>57.9605058</v>
       </c>
       <c r="Q61">
-        <v>113.58799737</v>
+        <v>113.4605058</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09832196982944527</v>
+        <v>0.09951981856133654</v>
       </c>
       <c r="T61">
-        <v>0.9619583223802242</v>
+        <v>0.9838973425719119</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.722411201815813</v>
+        <v>8.57703768178555</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06580892742453462</v>
+        <v>0.06573819721899668</v>
       </c>
       <c r="C62">
-        <v>185.8524417728812</v>
+        <v>184.1825031097371</v>
       </c>
       <c r="D62">
-        <v>358.5824417728812</v>
+        <v>359.854503109737</v>
       </c>
       <c r="E62">
-        <v>62.92</v>
+        <v>65.86200000000001</v>
       </c>
       <c r="F62">
-        <v>176.52</v>
+        <v>179.462</v>
       </c>
       <c r="G62">
         <v>3.79</v>
@@ -6365,28 +6365,28 @@
         <v>81</v>
       </c>
       <c r="M62">
-        <v>9.443819999999999</v>
+        <v>9.601217</v>
       </c>
       <c r="N62">
-        <v>71.55618</v>
+        <v>71.39878299999999</v>
       </c>
       <c r="O62">
-        <v>13.5956742</v>
+        <v>13.56576877</v>
       </c>
       <c r="P62">
-        <v>57.9605058</v>
+        <v>57.83301423</v>
       </c>
       <c r="Q62">
-        <v>113.4605058</v>
+        <v>113.33301423</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09951981856133654</v>
+        <v>0.1007790954333248</v>
       </c>
       <c r="T62">
-        <v>0.9838973425719119</v>
+        <v>1.006961440722148</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>8.57703768178555</v>
+        <v>8.436430506674309</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06573819721899668</v>
+        <v>0.06566746701345874</v>
       </c>
       <c r="C63">
-        <v>184.1825031097371</v>
+        <v>182.5216217823621</v>
       </c>
       <c r="D63">
-        <v>359.854503109737</v>
+        <v>361.1356217823621</v>
       </c>
       <c r="E63">
-        <v>65.86200000000001</v>
+        <v>68.80400000000002</v>
       </c>
       <c r="F63">
-        <v>179.462</v>
+        <v>182.404</v>
       </c>
       <c r="G63">
         <v>3.79</v>
@@ -6447,28 +6447,28 @@
         <v>81</v>
       </c>
       <c r="M63">
-        <v>9.601217</v>
+        <v>9.758614</v>
       </c>
       <c r="N63">
-        <v>71.39878299999999</v>
+        <v>71.24138600000001</v>
       </c>
       <c r="O63">
-        <v>13.56576877</v>
+        <v>13.53586334</v>
       </c>
       <c r="P63">
-        <v>57.83301423</v>
+        <v>57.70552266000001</v>
       </c>
       <c r="Q63">
-        <v>113.33301423</v>
+        <v>113.20552266</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1007790954333248</v>
+        <v>0.1021046500354177</v>
       </c>
       <c r="T63">
-        <v>1.006961440722148</v>
+        <v>1.031239438775028</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>8.436430506674309</v>
+        <v>8.300359046889241</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06566746701345874</v>
+        <v>0.06559673680792079</v>
       </c>
       <c r="C64">
-        <v>182.5216217823621</v>
+        <v>180.8698948714867</v>
       </c>
       <c r="D64">
-        <v>361.1356217823621</v>
+        <v>362.4258948714867</v>
       </c>
       <c r="E64">
-        <v>68.80400000000002</v>
+        <v>71.74600000000002</v>
       </c>
       <c r="F64">
-        <v>182.404</v>
+        <v>185.346</v>
       </c>
       <c r="G64">
         <v>3.79</v>
@@ -6529,28 +6529,28 @@
         <v>81</v>
       </c>
       <c r="M64">
-        <v>9.758614</v>
+        <v>9.916010999999999</v>
       </c>
       <c r="N64">
-        <v>71.24138600000001</v>
+        <v>71.083989</v>
       </c>
       <c r="O64">
-        <v>13.53586334</v>
+        <v>13.50595791</v>
       </c>
       <c r="P64">
-        <v>57.70552266000001</v>
+        <v>57.57803109</v>
       </c>
       <c r="Q64">
-        <v>113.20552266</v>
+        <v>113.07803109</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1021046500354177</v>
+        <v>0.1035018562376238</v>
       </c>
       <c r="T64">
-        <v>1.031239438775028</v>
+        <v>1.056829761046982</v>
       </c>
       <c r="U64">
         <v>0.0535</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>8.300359046889241</v>
+        <v>8.168607315986238</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.06559673680792079</v>
+        <v>0.06552600660238286</v>
       </c>
       <c r="C65">
-        <v>180.8698948714867</v>
+        <v>179.2274208502234</v>
       </c>
       <c r="D65">
-        <v>362.4258948714867</v>
+        <v>363.7254208502233</v>
       </c>
       <c r="E65">
-        <v>71.74600000000002</v>
+        <v>74.688</v>
       </c>
       <c r="F65">
-        <v>185.346</v>
+        <v>188.288</v>
       </c>
       <c r="G65">
         <v>3.79</v>
@@ -6611,28 +6611,28 @@
         <v>81</v>
       </c>
       <c r="M65">
-        <v>9.916010999999999</v>
+        <v>10.073408</v>
       </c>
       <c r="N65">
-        <v>71.083989</v>
+        <v>70.926592</v>
       </c>
       <c r="O65">
-        <v>13.50595791</v>
+        <v>13.47605248</v>
       </c>
       <c r="P65">
-        <v>57.57803109</v>
+        <v>57.45053952</v>
       </c>
       <c r="Q65">
-        <v>113.07803109</v>
+        <v>112.95053952</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1035018562376238</v>
+        <v>0.1049766850066191</v>
       </c>
       <c r="T65">
-        <v>1.056829761046982</v>
+        <v>1.083841767889601</v>
       </c>
       <c r="U65">
         <v>0.0535</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>8.168607315986238</v>
+        <v>8.040972826673952</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.06552600660238286</v>
+        <v>0.06545527639684492</v>
       </c>
       <c r="C66">
-        <v>179.2274208502234</v>
+        <v>177.5942996091219</v>
       </c>
       <c r="D66">
-        <v>363.7254208502233</v>
+        <v>365.0342996091219</v>
       </c>
       <c r="E66">
-        <v>74.688</v>
+        <v>77.63000000000001</v>
       </c>
       <c r="F66">
-        <v>188.288</v>
+        <v>191.23</v>
       </c>
       <c r="G66">
         <v>3.79</v>
@@ -6693,28 +6693,28 @@
         <v>81</v>
       </c>
       <c r="M66">
-        <v>10.073408</v>
+        <v>10.230805</v>
       </c>
       <c r="N66">
-        <v>70.926592</v>
+        <v>70.769195</v>
       </c>
       <c r="O66">
-        <v>13.47605248</v>
+        <v>13.44614705</v>
       </c>
       <c r="P66">
-        <v>57.45053952</v>
+        <v>57.32304795</v>
       </c>
       <c r="Q66">
-        <v>112.95053952</v>
+        <v>112.82304795</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1049766850066191</v>
+        <v>0.1065357897052712</v>
       </c>
       <c r="T66">
-        <v>1.083841767889601</v>
+        <v>1.112397317980369</v>
       </c>
       <c r="U66">
         <v>0.0535</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>8.040972826673952</v>
+        <v>7.91726555241743</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.06545527639684492</v>
+        <v>0.06538454619130697</v>
       </c>
       <c r="C67">
-        <v>177.5942996091219</v>
+        <v>175.9706324817629</v>
       </c>
       <c r="D67">
-        <v>365.0342996091219</v>
+        <v>366.3526324817628</v>
       </c>
       <c r="E67">
-        <v>77.63000000000001</v>
+        <v>80.57200000000002</v>
       </c>
       <c r="F67">
-        <v>191.23</v>
+        <v>194.172</v>
       </c>
       <c r="G67">
         <v>3.79</v>
@@ -6775,28 +6775,28 @@
         <v>81</v>
       </c>
       <c r="M67">
-        <v>10.230805</v>
+        <v>10.388202</v>
       </c>
       <c r="N67">
-        <v>70.769195</v>
+        <v>70.61179799999999</v>
       </c>
       <c r="O67">
-        <v>13.44614705</v>
+        <v>13.41624162</v>
       </c>
       <c r="P67">
-        <v>57.32304795</v>
+        <v>57.19555637999999</v>
       </c>
       <c r="Q67">
-        <v>112.82304795</v>
+        <v>112.69555638</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1065357897052712</v>
+        <v>0.1081866064450205</v>
       </c>
       <c r="T67">
-        <v>1.112397317980369</v>
+        <v>1.14263260631177</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.91726555241743</v>
+        <v>7.797306983441407</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.06538454619130697</v>
+        <v>0.06531381598576903</v>
       </c>
       <c r="C68">
-        <v>175.9706324817629</v>
+        <v>174.3565222709101</v>
       </c>
       <c r="D68">
-        <v>366.3526324817628</v>
+        <v>367.68052227091</v>
       </c>
       <c r="E68">
-        <v>80.57200000000002</v>
+        <v>83.51400000000002</v>
       </c>
       <c r="F68">
-        <v>194.172</v>
+        <v>197.114</v>
       </c>
       <c r="G68">
         <v>3.79</v>
@@ -6857,28 +6857,28 @@
         <v>81</v>
       </c>
       <c r="M68">
-        <v>10.388202</v>
+        <v>10.545599</v>
       </c>
       <c r="N68">
-        <v>70.61179799999999</v>
+        <v>70.454401</v>
       </c>
       <c r="O68">
-        <v>13.41624162</v>
+        <v>13.38633619</v>
       </c>
       <c r="P68">
-        <v>57.19555637999999</v>
+        <v>57.06806481</v>
       </c>
       <c r="Q68">
-        <v>112.69555638</v>
+        <v>112.56806481</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1081866064450205</v>
+        <v>0.1099374726841486</v>
       </c>
       <c r="T68">
-        <v>1.14263260631177</v>
+        <v>1.174700336360227</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.797306983441407</v>
+        <v>7.680929267270641</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.06531381598576903</v>
+        <v>0.0656837257802311</v>
       </c>
       <c r="C69">
-        <v>174.3565222709101</v>
+        <v>164.5743240140943</v>
       </c>
       <c r="D69">
-        <v>367.68052227091</v>
+        <v>360.8403240140943</v>
       </c>
       <c r="E69">
-        <v>83.51400000000002</v>
+        <v>86.45600000000003</v>
       </c>
       <c r="F69">
-        <v>197.114</v>
+        <v>200.056</v>
       </c>
       <c r="G69">
         <v>3.79</v>
@@ -6939,45 +6939,45 @@
         <v>81</v>
       </c>
       <c r="M69">
-        <v>10.545599</v>
+        <v>10.8630408</v>
       </c>
       <c r="N69">
-        <v>70.454401</v>
+        <v>70.13695920000001</v>
       </c>
       <c r="O69">
-        <v>13.38633619</v>
+        <v>13.326022248</v>
       </c>
       <c r="P69">
-        <v>57.06806481</v>
+        <v>56.81093695200001</v>
       </c>
       <c r="Q69">
-        <v>112.56806481</v>
+        <v>112.310936952</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1099374726841486</v>
+        <v>0.1117977680632222</v>
       </c>
       <c r="T69">
-        <v>1.174700336360227</v>
+        <v>1.208772299536711</v>
       </c>
       <c r="U69">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V69">
         <v>0.19</v>
       </c>
       <c r="W69">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y69">
-        <v>7.680929267270641</v>
+        <v>7.456475722709244</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0656837257802311</v>
+        <v>0.06561947557469315</v>
       </c>
       <c r="C70">
-        <v>164.5743240140943</v>
+        <v>162.8020857919433</v>
       </c>
       <c r="D70">
-        <v>360.8403240140943</v>
+        <v>362.0100857919433</v>
       </c>
       <c r="E70">
-        <v>86.45600000000003</v>
+        <v>89.39800000000004</v>
       </c>
       <c r="F70">
-        <v>200.056</v>
+        <v>202.998</v>
       </c>
       <c r="G70">
         <v>3.79</v>
@@ -7021,28 +7021,28 @@
         <v>81</v>
       </c>
       <c r="M70">
-        <v>10.8630408</v>
+        <v>11.0227914</v>
       </c>
       <c r="N70">
-        <v>70.13695920000001</v>
+        <v>69.9772086</v>
       </c>
       <c r="O70">
-        <v>13.326022248</v>
+        <v>13.295669634</v>
       </c>
       <c r="P70">
-        <v>56.81093695200001</v>
+        <v>56.681538966</v>
       </c>
       <c r="Q70">
-        <v>112.310936952</v>
+        <v>112.181538966</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1117977680632222</v>
+        <v>0.1137780824990102</v>
       </c>
       <c r="T70">
-        <v>1.208772299536711</v>
+        <v>1.245042453885873</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>7.456475722709244</v>
+        <v>7.348410857162732</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.06561947557469315</v>
+        <v>0.0655552253691552</v>
       </c>
       <c r="C71">
-        <v>162.8020857919433</v>
+        <v>161.0374564361303</v>
       </c>
       <c r="D71">
-        <v>362.0100857919433</v>
+        <v>363.1874564361303</v>
       </c>
       <c r="E71">
-        <v>89.39800000000004</v>
+        <v>92.34000000000002</v>
       </c>
       <c r="F71">
-        <v>202.998</v>
+        <v>205.94</v>
       </c>
       <c r="G71">
         <v>3.79</v>
@@ -7103,28 +7103,28 @@
         <v>81</v>
       </c>
       <c r="M71">
-        <v>11.0227914</v>
+        <v>11.182542</v>
       </c>
       <c r="N71">
-        <v>69.9772086</v>
+        <v>69.817458</v>
       </c>
       <c r="O71">
-        <v>13.295669634</v>
+        <v>13.26531702</v>
       </c>
       <c r="P71">
-        <v>56.681538966</v>
+        <v>56.55214098</v>
       </c>
       <c r="Q71">
-        <v>112.181538966</v>
+        <v>112.05214098</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1137780824990102</v>
+        <v>0.115890417897184</v>
       </c>
       <c r="T71">
-        <v>1.245042453885873</v>
+        <v>1.283730618524978</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>7.348410857162732</v>
+        <v>7.243433559203265</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0655552253691552</v>
+        <v>0.06549097516361728</v>
       </c>
       <c r="C72">
-        <v>161.0374564361303</v>
+        <v>159.2805104281709</v>
       </c>
       <c r="D72">
-        <v>363.1874564361303</v>
+        <v>364.3725104281709</v>
       </c>
       <c r="E72">
-        <v>92.34000000000002</v>
+        <v>95.28200000000002</v>
       </c>
       <c r="F72">
-        <v>205.94</v>
+        <v>208.882</v>
       </c>
       <c r="G72">
         <v>3.79</v>
@@ -7185,28 +7185,28 @@
         <v>81</v>
       </c>
       <c r="M72">
-        <v>11.182542</v>
+        <v>11.3422926</v>
       </c>
       <c r="N72">
-        <v>69.817458</v>
+        <v>69.65770739999999</v>
       </c>
       <c r="O72">
-        <v>13.26531702</v>
+        <v>13.234964406</v>
       </c>
       <c r="P72">
-        <v>56.55214098</v>
+        <v>56.42274299399999</v>
       </c>
       <c r="Q72">
-        <v>112.05214098</v>
+        <v>111.922742994</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.115890417897184</v>
+        <v>0.1181484315986803</v>
       </c>
       <c r="T72">
-        <v>1.283730618524978</v>
+        <v>1.325086932449539</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>7.243433559203265</v>
+        <v>7.14141336822857</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.06549097516361727</v>
+        <v>0.06542672495807933</v>
       </c>
       <c r="C73">
-        <v>159.2805104281712</v>
+        <v>157.5313232248751</v>
       </c>
       <c r="D73">
-        <v>364.3725104281712</v>
+        <v>365.565323224875</v>
       </c>
       <c r="E73">
-        <v>95.282</v>
+        <v>98.224</v>
       </c>
       <c r="F73">
-        <v>208.882</v>
+        <v>211.824</v>
       </c>
       <c r="G73">
         <v>3.79</v>
@@ -7267,28 +7267,28 @@
         <v>81</v>
       </c>
       <c r="M73">
-        <v>11.3422926</v>
+        <v>11.5020432</v>
       </c>
       <c r="N73">
-        <v>69.65770740000001</v>
+        <v>69.4979568</v>
       </c>
       <c r="O73">
-        <v>13.234964406</v>
+        <v>13.204611792</v>
       </c>
       <c r="P73">
-        <v>56.422742994</v>
+        <v>56.293345008</v>
       </c>
       <c r="Q73">
-        <v>111.922742994</v>
+        <v>111.793345008</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1181484315986802</v>
+        <v>0.1205677319931404</v>
       </c>
       <c r="T73">
-        <v>1.325086932449538</v>
+        <v>1.369397268797282</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>7.141413368228573</v>
+        <v>7.042227071447619</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.06542672495807933</v>
+        <v>0.06536247475254139</v>
       </c>
       <c r="C74">
-        <v>157.5313232248751</v>
+        <v>155.7899712743601</v>
       </c>
       <c r="D74">
-        <v>365.565323224875</v>
+        <v>366.7659712743601</v>
       </c>
       <c r="E74">
-        <v>98.224</v>
+        <v>101.166</v>
       </c>
       <c r="F74">
-        <v>211.824</v>
+        <v>214.766</v>
       </c>
       <c r="G74">
         <v>3.79</v>
@@ -7349,28 +7349,28 @@
         <v>81</v>
       </c>
       <c r="M74">
-        <v>11.5020432</v>
+        <v>11.6617938</v>
       </c>
       <c r="N74">
-        <v>69.4979568</v>
+        <v>69.3382062</v>
       </c>
       <c r="O74">
-        <v>13.204611792</v>
+        <v>13.174259178</v>
       </c>
       <c r="P74">
-        <v>56.293345008</v>
+        <v>56.163947022</v>
       </c>
       <c r="Q74">
-        <v>111.793345008</v>
+        <v>111.663947022</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1205677319931404</v>
+        <v>0.1231662398242274</v>
       </c>
       <c r="T74">
-        <v>1.369397268797282</v>
+        <v>1.416989852281896</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>7.042227071447619</v>
+        <v>6.945758207455186</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.06536247475254139</v>
+        <v>0.06529822454700343</v>
       </c>
       <c r="C75">
-        <v>155.7899712743601</v>
+        <v>154.0565320323872</v>
       </c>
       <c r="D75">
-        <v>366.7659712743601</v>
+        <v>367.9745320323872</v>
       </c>
       <c r="E75">
-        <v>101.166</v>
+        <v>104.108</v>
       </c>
       <c r="F75">
-        <v>214.766</v>
+        <v>217.708</v>
       </c>
       <c r="G75">
         <v>3.79</v>
@@ -7431,28 +7431,28 @@
         <v>81</v>
       </c>
       <c r="M75">
-        <v>11.6617938</v>
+        <v>11.8215444</v>
       </c>
       <c r="N75">
-        <v>69.3382062</v>
+        <v>69.17845560000001</v>
       </c>
       <c r="O75">
-        <v>13.174259178</v>
+        <v>13.143906564</v>
       </c>
       <c r="P75">
-        <v>56.163947022</v>
+        <v>56.034549036</v>
       </c>
       <c r="Q75">
-        <v>111.663947022</v>
+        <v>111.534549036</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1231662398242274</v>
+        <v>0.1259646328730901</v>
       </c>
       <c r="T75">
-        <v>1.416989852281896</v>
+        <v>1.468243403726864</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.945758207455186</v>
+        <v>6.851896610057143</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.06529822454700343</v>
+        <v>0.06523397434146549</v>
       </c>
       <c r="C76">
-        <v>154.0565320323872</v>
+        <v>152.3310839790141</v>
       </c>
       <c r="D76">
-        <v>367.9745320323872</v>
+        <v>369.191083979014</v>
       </c>
       <c r="E76">
-        <v>104.108</v>
+        <v>107.05</v>
       </c>
       <c r="F76">
-        <v>217.708</v>
+        <v>220.65</v>
       </c>
       <c r="G76">
         <v>3.79</v>
@@ -7513,28 +7513,28 @@
         <v>81</v>
       </c>
       <c r="M76">
-        <v>11.8215444</v>
+        <v>11.981295</v>
       </c>
       <c r="N76">
-        <v>69.17845560000001</v>
+        <v>69.018705</v>
       </c>
       <c r="O76">
-        <v>13.143906564</v>
+        <v>13.11355395</v>
       </c>
       <c r="P76">
-        <v>56.034549036</v>
+        <v>55.90515105</v>
       </c>
       <c r="Q76">
-        <v>111.534549036</v>
+        <v>111.40515105</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1259646328730901</v>
+        <v>0.128986897365862</v>
       </c>
       <c r="T76">
-        <v>1.468243403726864</v>
+        <v>1.52359723928743</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.851896610057143</v>
+        <v>6.760537988589714</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.06523397434146549</v>
+        <v>0.06516972413592756</v>
       </c>
       <c r="C77">
-        <v>152.3310839790141</v>
+        <v>150.613706635587</v>
       </c>
       <c r="D77">
-        <v>369.191083979014</v>
+        <v>370.415706635587</v>
       </c>
       <c r="E77">
-        <v>107.05</v>
+        <v>109.992</v>
       </c>
       <c r="F77">
-        <v>220.65</v>
+        <v>223.592</v>
       </c>
       <c r="G77">
         <v>3.79</v>
@@ -7595,28 +7595,28 @@
         <v>81</v>
       </c>
       <c r="M77">
-        <v>11.981295</v>
+        <v>12.1410456</v>
       </c>
       <c r="N77">
-        <v>69.018705</v>
+        <v>68.8589544</v>
       </c>
       <c r="O77">
-        <v>13.11355395</v>
+        <v>13.083201336</v>
       </c>
       <c r="P77">
-        <v>55.90515105</v>
+        <v>55.775753064</v>
       </c>
       <c r="Q77">
-        <v>111.40515105</v>
+        <v>111.275753064</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.128986897365862</v>
+        <v>0.1322610172330315</v>
       </c>
       <c r="T77">
-        <v>1.52359723928743</v>
+        <v>1.583563894478043</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.760537988589714</v>
+        <v>6.671583541371429</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.06516972413592756</v>
+        <v>0.06510547393038962</v>
       </c>
       <c r="C78">
-        <v>150.613706635587</v>
+        <v>148.9044805820661</v>
       </c>
       <c r="D78">
-        <v>370.415706635587</v>
+        <v>371.6484805820661</v>
       </c>
       <c r="E78">
-        <v>109.992</v>
+        <v>112.934</v>
       </c>
       <c r="F78">
-        <v>223.592</v>
+        <v>226.534</v>
       </c>
       <c r="G78">
         <v>3.79</v>
@@ -7677,28 +7677,28 @@
         <v>81</v>
       </c>
       <c r="M78">
-        <v>12.1410456</v>
+        <v>12.3007962</v>
       </c>
       <c r="N78">
-        <v>68.8589544</v>
+        <v>68.69920379999999</v>
       </c>
       <c r="O78">
-        <v>13.083201336</v>
+        <v>13.052848722</v>
       </c>
       <c r="P78">
-        <v>55.775753064</v>
+        <v>55.64635507799999</v>
       </c>
       <c r="Q78">
-        <v>111.275753064</v>
+        <v>111.146355078</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1322610172330315</v>
+        <v>0.1358198431756071</v>
       </c>
       <c r="T78">
-        <v>1.583563894478043</v>
+        <v>1.648745041424362</v>
       </c>
       <c r="U78">
         <v>0.0543</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>6.671583541371429</v>
+        <v>6.584939599275695</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.06510547393038962</v>
+        <v>0.06504122372485169</v>
       </c>
       <c r="C79">
-        <v>148.9044805820661</v>
+        <v>147.2034874747004</v>
       </c>
       <c r="D79">
-        <v>371.6484805820661</v>
+        <v>372.8894874747004</v>
       </c>
       <c r="E79">
-        <v>112.934</v>
+        <v>115.876</v>
       </c>
       <c r="F79">
-        <v>226.534</v>
+        <v>229.476</v>
       </c>
       <c r="G79">
         <v>3.79</v>
@@ -7759,28 +7759,28 @@
         <v>81</v>
       </c>
       <c r="M79">
-        <v>12.3007962</v>
+        <v>12.4605468</v>
       </c>
       <c r="N79">
-        <v>68.69920379999999</v>
+        <v>68.5394532</v>
       </c>
       <c r="O79">
-        <v>13.052848722</v>
+        <v>13.022496108</v>
       </c>
       <c r="P79">
-        <v>55.64635507799999</v>
+        <v>55.516957092</v>
       </c>
       <c r="Q79">
-        <v>111.146355078</v>
+        <v>111.016957092</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1358198431756071</v>
+        <v>0.1397021987493259</v>
       </c>
       <c r="T79">
-        <v>1.648745041424362</v>
+        <v>1.719851747183983</v>
       </c>
       <c r="U79">
         <v>0.0543</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>6.584939599275695</v>
+        <v>6.500517296720879</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.06504122372485169</v>
+        <v>0.06497697351931375</v>
       </c>
       <c r="C80">
-        <v>147.2034874747004</v>
+        <v>145.5108100640576</v>
       </c>
       <c r="D80">
-        <v>372.8894874747004</v>
+        <v>374.1388100640576</v>
       </c>
       <c r="E80">
-        <v>115.876</v>
+        <v>118.818</v>
       </c>
       <c r="F80">
-        <v>229.476</v>
+        <v>232.418</v>
       </c>
       <c r="G80">
         <v>3.79</v>
@@ -7841,28 +7841,28 @@
         <v>81</v>
       </c>
       <c r="M80">
-        <v>12.4605468</v>
+        <v>12.6202974</v>
       </c>
       <c r="N80">
-        <v>68.5394532</v>
+        <v>68.3797026</v>
       </c>
       <c r="O80">
-        <v>13.022496108</v>
+        <v>12.992143494</v>
       </c>
       <c r="P80">
-        <v>55.516957092</v>
+        <v>55.387559106</v>
       </c>
       <c r="Q80">
-        <v>111.016957092</v>
+        <v>110.887559106</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1397021987493259</v>
+        <v>0.1439543024729226</v>
       </c>
       <c r="T80">
-        <v>1.719851747183983</v>
+        <v>1.797730520158805</v>
       </c>
       <c r="U80">
         <v>0.0543</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>6.500517296720879</v>
+        <v>6.418232267648463</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.06497697351931375</v>
+        <v>0.06491272331377579</v>
       </c>
       <c r="C81">
-        <v>145.5108100640576</v>
+        <v>143.8265322134187</v>
       </c>
       <c r="D81">
-        <v>374.1388100640576</v>
+        <v>375.3965322134187</v>
       </c>
       <c r="E81">
-        <v>118.818</v>
+        <v>121.76</v>
       </c>
       <c r="F81">
-        <v>232.418</v>
+        <v>235.36</v>
       </c>
       <c r="G81">
         <v>3.79</v>
@@ -7923,28 +7923,28 @@
         <v>81</v>
       </c>
       <c r="M81">
-        <v>12.6202974</v>
+        <v>12.780048</v>
       </c>
       <c r="N81">
-        <v>68.3797026</v>
+        <v>68.21995200000001</v>
       </c>
       <c r="O81">
-        <v>12.992143494</v>
+        <v>12.96179088</v>
       </c>
       <c r="P81">
-        <v>55.387559106</v>
+        <v>55.25816112</v>
       </c>
       <c r="Q81">
-        <v>110.887559106</v>
+        <v>110.75816112</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1439543024729226</v>
+        <v>0.148631616568879</v>
       </c>
       <c r="T81">
-        <v>1.797730520158805</v>
+        <v>1.88339717043111</v>
       </c>
       <c r="U81">
         <v>0.0543</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>6.418232267648463</v>
+        <v>6.338004364302857</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.06491272331377579</v>
+        <v>0.06484847310823785</v>
       </c>
       <c r="C82">
-        <v>143.8265322134187</v>
+        <v>142.1507389175408</v>
       </c>
       <c r="D82">
-        <v>375.3965322134187</v>
+        <v>376.6627389175408</v>
       </c>
       <c r="E82">
-        <v>121.76</v>
+        <v>124.702</v>
       </c>
       <c r="F82">
-        <v>235.36</v>
+        <v>238.302</v>
       </c>
       <c r="G82">
         <v>3.79</v>
@@ -8005,28 +8005,28 @@
         <v>81</v>
       </c>
       <c r="M82">
-        <v>12.780048</v>
+        <v>12.9397986</v>
       </c>
       <c r="N82">
-        <v>68.21995200000001</v>
+        <v>68.0602014</v>
       </c>
       <c r="O82">
-        <v>12.96179088</v>
+        <v>12.931438266</v>
       </c>
       <c r="P82">
-        <v>55.25816112</v>
+        <v>55.128763134</v>
       </c>
       <c r="Q82">
-        <v>110.75816112</v>
+        <v>110.628763134</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.148631616568879</v>
+        <v>0.1538012795170414</v>
       </c>
       <c r="T82">
-        <v>1.88339717043111</v>
+        <v>1.978081362837341</v>
       </c>
       <c r="U82">
         <v>0.0543</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>6.338004364302857</v>
+        <v>6.259757396842327</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.06484847310823785</v>
+        <v>0.06478422290269992</v>
       </c>
       <c r="C83">
-        <v>142.1507389175408</v>
+        <v>140.483516321808</v>
       </c>
       <c r="D83">
-        <v>376.6627389175408</v>
+        <v>377.937516321808</v>
       </c>
       <c r="E83">
-        <v>124.702</v>
+        <v>127.644</v>
       </c>
       <c r="F83">
-        <v>238.302</v>
+        <v>241.244</v>
       </c>
       <c r="G83">
         <v>3.79</v>
@@ -8087,28 +8087,28 @@
         <v>81</v>
       </c>
       <c r="M83">
-        <v>12.9397986</v>
+        <v>13.0995492</v>
       </c>
       <c r="N83">
-        <v>68.0602014</v>
+        <v>67.9004508</v>
       </c>
       <c r="O83">
-        <v>12.931438266</v>
+        <v>12.901085652</v>
       </c>
       <c r="P83">
-        <v>55.128763134</v>
+        <v>54.999365148</v>
       </c>
       <c r="Q83">
-        <v>110.628763134</v>
+        <v>110.499365148</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1538012795170414</v>
+        <v>0.159545349459444</v>
       </c>
       <c r="T83">
-        <v>1.978081362837341</v>
+        <v>2.083286021066487</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>6.259757396842327</v>
+        <v>6.183418892002788</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.06478422290269992</v>
+        <v>0.06539227269716198</v>
       </c>
       <c r="C84">
-        <v>140.483516321808</v>
+        <v>125.8121558402</v>
       </c>
       <c r="D84">
-        <v>377.937516321808</v>
+        <v>366.2081558402</v>
       </c>
       <c r="E84">
-        <v>127.644</v>
+        <v>130.586</v>
       </c>
       <c r="F84">
-        <v>241.244</v>
+        <v>244.186</v>
       </c>
       <c r="G84">
         <v>3.79</v>
@@ -8169,45 +8169,45 @@
         <v>81</v>
       </c>
       <c r="M84">
-        <v>13.0995492</v>
+        <v>13.5034858</v>
       </c>
       <c r="N84">
-        <v>67.9004508</v>
+        <v>67.49651420000001</v>
       </c>
       <c r="O84">
-        <v>12.901085652</v>
+        <v>12.824337698</v>
       </c>
       <c r="P84">
-        <v>54.999365148</v>
+        <v>54.67217650200001</v>
       </c>
       <c r="Q84">
-        <v>110.499365148</v>
+        <v>110.172176502</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.159545349459444</v>
+        <v>0.165965192336247</v>
       </c>
       <c r="T84">
-        <v>2.083286021066487</v>
+        <v>2.200867697910827</v>
       </c>
       <c r="U84">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V84">
         <v>0.19</v>
       </c>
       <c r="W84">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y84">
-        <v>6.183418892002788</v>
+        <v>5.998451155478684</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.06539227269716198</v>
+        <v>0.06533612249162404</v>
       </c>
       <c r="C85">
-        <v>125.8121558402</v>
+        <v>123.9227016168204</v>
       </c>
       <c r="D85">
-        <v>366.2081558402</v>
+        <v>367.2607016168204</v>
       </c>
       <c r="E85">
-        <v>130.586</v>
+        <v>133.528</v>
       </c>
       <c r="F85">
-        <v>244.186</v>
+        <v>247.128</v>
       </c>
       <c r="G85">
         <v>3.79</v>
@@ -8251,28 +8251,28 @@
         <v>81</v>
       </c>
       <c r="M85">
-        <v>13.5034858</v>
+        <v>13.6661784</v>
       </c>
       <c r="N85">
-        <v>67.49651420000001</v>
+        <v>67.33382159999999</v>
       </c>
       <c r="O85">
-        <v>12.824337698</v>
+        <v>12.793426104</v>
       </c>
       <c r="P85">
-        <v>54.67217650200001</v>
+        <v>54.540395496</v>
       </c>
       <c r="Q85">
-        <v>110.172176502</v>
+        <v>110.040395496</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.165965192336247</v>
+        <v>0.1731875155726503</v>
       </c>
       <c r="T85">
-        <v>2.200867697910827</v>
+        <v>2.333147084360709</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.998451155478684</v>
+        <v>5.927041022675366</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.06533612249162404</v>
+        <v>0.0652799722860861</v>
       </c>
       <c r="C86">
-        <v>123.9227016168205</v>
+        <v>122.0393152318162</v>
       </c>
       <c r="D86">
-        <v>367.2607016168204</v>
+        <v>368.3193152318162</v>
       </c>
       <c r="E86">
-        <v>133.528</v>
+        <v>136.47</v>
       </c>
       <c r="F86">
-        <v>247.128</v>
+        <v>250.07</v>
       </c>
       <c r="G86">
         <v>3.79</v>
@@ -8333,28 +8333,28 @@
         <v>81</v>
       </c>
       <c r="M86">
-        <v>13.6661784</v>
+        <v>13.828871</v>
       </c>
       <c r="N86">
-        <v>67.33382159999999</v>
+        <v>67.17112900000001</v>
       </c>
       <c r="O86">
-        <v>12.793426104</v>
+        <v>12.76251451</v>
       </c>
       <c r="P86">
-        <v>54.540395496</v>
+        <v>54.40861449000001</v>
       </c>
       <c r="Q86">
-        <v>110.040395496</v>
+        <v>109.90861449</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1731875155726502</v>
+        <v>0.1813728152405739</v>
       </c>
       <c r="T86">
-        <v>2.333147084360708</v>
+        <v>2.48306372233724</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.927041022675366</v>
+        <v>5.85731112829095</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.0652799722860861</v>
+        <v>0.06522382208054817</v>
       </c>
       <c r="C87">
-        <v>122.0393152318162</v>
+        <v>120.162049307741</v>
       </c>
       <c r="D87">
-        <v>368.3193152318162</v>
+        <v>369.384049307741</v>
       </c>
       <c r="E87">
-        <v>136.47</v>
+        <v>139.412</v>
       </c>
       <c r="F87">
-        <v>250.07</v>
+        <v>253.012</v>
       </c>
       <c r="G87">
         <v>3.79</v>
@@ -8415,28 +8415,28 @@
         <v>81</v>
       </c>
       <c r="M87">
-        <v>13.828871</v>
+        <v>13.9915636</v>
       </c>
       <c r="N87">
-        <v>67.17112900000001</v>
+        <v>67.00843639999999</v>
       </c>
       <c r="O87">
-        <v>12.76251451</v>
+        <v>12.731602916</v>
       </c>
       <c r="P87">
-        <v>54.40861449000001</v>
+        <v>54.27683348399999</v>
       </c>
       <c r="Q87">
-        <v>109.90861449</v>
+        <v>109.776833484</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1813728152405739</v>
+        <v>0.1907274434324868</v>
       </c>
       <c r="T87">
-        <v>2.48306372233724</v>
+        <v>2.65439702288185</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.85731112829095</v>
+        <v>5.789202859357333</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.06522382208054817</v>
+        <v>0.06516767187501021</v>
       </c>
       <c r="C88">
-        <v>120.162049307741</v>
+        <v>118.2909570773957</v>
       </c>
       <c r="D88">
-        <v>369.384049307741</v>
+        <v>370.4549570773956</v>
       </c>
       <c r="E88">
-        <v>139.412</v>
+        <v>142.354</v>
       </c>
       <c r="F88">
-        <v>253.012</v>
+        <v>255.954</v>
       </c>
       <c r="G88">
         <v>3.79</v>
@@ -8497,28 +8497,28 @@
         <v>81</v>
       </c>
       <c r="M88">
-        <v>13.9915636</v>
+        <v>14.1542562</v>
       </c>
       <c r="N88">
-        <v>67.00843639999999</v>
+        <v>66.84574380000001</v>
       </c>
       <c r="O88">
-        <v>12.731602916</v>
+        <v>12.700691322</v>
       </c>
       <c r="P88">
-        <v>54.27683348399999</v>
+        <v>54.14505247800001</v>
       </c>
       <c r="Q88">
-        <v>109.776833484</v>
+        <v>109.645052478</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1907274434324868</v>
+        <v>0.2015212451923862</v>
       </c>
       <c r="T88">
-        <v>2.65439702288185</v>
+        <v>2.852089292741014</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.789202859357333</v>
+        <v>5.722660297755527</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.06516767187501021</v>
+        <v>0.06511152166947227</v>
       </c>
       <c r="C89">
-        <v>118.2909570773957</v>
+        <v>116.4260923926994</v>
       </c>
       <c r="D89">
-        <v>370.4549570773956</v>
+        <v>371.5320923926994</v>
       </c>
       <c r="E89">
-        <v>142.354</v>
+        <v>145.296</v>
       </c>
       <c r="F89">
-        <v>255.954</v>
+        <v>258.896</v>
       </c>
       <c r="G89">
         <v>3.79</v>
@@ -8579,28 +8579,28 @@
         <v>81</v>
       </c>
       <c r="M89">
-        <v>14.1542562</v>
+        <v>14.3169488</v>
       </c>
       <c r="N89">
-        <v>66.84574380000001</v>
+        <v>66.68305119999999</v>
       </c>
       <c r="O89">
-        <v>12.700691322</v>
+        <v>12.669779728</v>
       </c>
       <c r="P89">
-        <v>54.14505247800001</v>
+        <v>54.013271472</v>
       </c>
       <c r="Q89">
-        <v>109.645052478</v>
+        <v>109.513271472</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2015212451923862</v>
+        <v>0.2141140139122689</v>
       </c>
       <c r="T89">
-        <v>2.852089292741014</v>
+        <v>3.082730274243373</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.722660297755527</v>
+        <v>5.657630067099213</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.06511152166947227</v>
+        <v>0.06505537146393434</v>
       </c>
       <c r="C90">
-        <v>116.4260923926994</v>
+        <v>114.5675097337186</v>
       </c>
       <c r="D90">
-        <v>371.5320923926994</v>
+        <v>372.6155097337185</v>
       </c>
       <c r="E90">
-        <v>145.296</v>
+        <v>148.238</v>
       </c>
       <c r="F90">
-        <v>258.896</v>
+        <v>261.838</v>
       </c>
       <c r="G90">
         <v>3.79</v>
@@ -8661,28 +8661,28 @@
         <v>81</v>
       </c>
       <c r="M90">
-        <v>14.3169488</v>
+        <v>14.4796414</v>
       </c>
       <c r="N90">
-        <v>66.68305119999999</v>
+        <v>66.52035860000001</v>
       </c>
       <c r="O90">
-        <v>12.669779728</v>
+        <v>12.638868134</v>
       </c>
       <c r="P90">
-        <v>54.013271472</v>
+        <v>53.881490466</v>
       </c>
       <c r="Q90">
-        <v>109.513271472</v>
+        <v>109.381490466</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2141140139122689</v>
+        <v>0.2289963769448576</v>
       </c>
       <c r="T90">
-        <v>3.082730274243373</v>
+        <v>3.35530597965525</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.657630067099213</v>
+        <v>5.594061189940796</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.06505537146393434</v>
+        <v>0.0649992212583964</v>
       </c>
       <c r="C91">
-        <v>114.5675097337186</v>
+        <v>112.7152642178502</v>
       </c>
       <c r="D91">
-        <v>372.6155097337185</v>
+        <v>373.7052642178502</v>
       </c>
       <c r="E91">
-        <v>148.238</v>
+        <v>151.18</v>
       </c>
       <c r="F91">
-        <v>261.838</v>
+        <v>264.78</v>
       </c>
       <c r="G91">
         <v>3.79</v>
@@ -8743,28 +8743,28 @@
         <v>81</v>
       </c>
       <c r="M91">
-        <v>14.4796414</v>
+        <v>14.642334</v>
       </c>
       <c r="N91">
-        <v>66.52035860000001</v>
+        <v>66.35766599999999</v>
       </c>
       <c r="O91">
-        <v>12.638868134</v>
+        <v>12.60795654</v>
       </c>
       <c r="P91">
-        <v>53.881490466</v>
+        <v>53.74970945999999</v>
       </c>
       <c r="Q91">
-        <v>109.381490466</v>
+        <v>109.24970946</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2289963769448576</v>
+        <v>0.246855212583964</v>
       </c>
       <c r="T91">
-        <v>3.35530597965525</v>
+        <v>3.682396826149505</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.594061189940796</v>
+        <v>5.531904954497008</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.0649992212583964</v>
+        <v>0.06494307105285846</v>
       </c>
       <c r="C92">
-        <v>112.7152642178502</v>
+        <v>110.8694116091701</v>
       </c>
       <c r="D92">
-        <v>373.7052642178502</v>
+        <v>374.80141160917</v>
       </c>
       <c r="E92">
-        <v>151.18</v>
+        <v>154.122</v>
       </c>
       <c r="F92">
-        <v>264.78</v>
+        <v>267.722</v>
       </c>
       <c r="G92">
         <v>3.79</v>
@@ -8825,28 +8825,28 @@
         <v>81</v>
       </c>
       <c r="M92">
-        <v>14.642334</v>
+        <v>14.8050266</v>
       </c>
       <c r="N92">
-        <v>66.35766599999999</v>
+        <v>66.19497339999999</v>
       </c>
       <c r="O92">
-        <v>12.60795654</v>
+        <v>12.577044946</v>
       </c>
       <c r="P92">
-        <v>53.74970945999999</v>
+        <v>53.61792845399999</v>
       </c>
       <c r="Q92">
-        <v>109.24970946</v>
+        <v>109.117928454</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.246855212583964</v>
+        <v>0.2686826783650939</v>
       </c>
       <c r="T92">
-        <v>3.682396826149505</v>
+        <v>4.082174527420259</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.531904954497008</v>
+        <v>5.471114790161876</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.06494307105285846</v>
+        <v>0.06488692084732051</v>
       </c>
       <c r="C93">
-        <v>110.8694116091701</v>
+        <v>109.0300083279449</v>
       </c>
       <c r="D93">
-        <v>374.80141160917</v>
+        <v>375.9040083279448</v>
       </c>
       <c r="E93">
-        <v>154.122</v>
+        <v>157.064</v>
       </c>
       <c r="F93">
-        <v>267.722</v>
+        <v>270.664</v>
       </c>
       <c r="G93">
         <v>3.79</v>
@@ -8907,28 +8907,28 @@
         <v>81</v>
       </c>
       <c r="M93">
-        <v>14.8050266</v>
+        <v>14.9677192</v>
       </c>
       <c r="N93">
-        <v>66.19497339999999</v>
+        <v>66.0322808</v>
       </c>
       <c r="O93">
-        <v>12.577044946</v>
+        <v>12.546133352</v>
       </c>
       <c r="P93">
-        <v>53.61792845399999</v>
+        <v>53.486147448</v>
       </c>
       <c r="Q93">
-        <v>109.117928454</v>
+        <v>108.986147448</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2686826783650939</v>
+        <v>0.2959670105915065</v>
       </c>
       <c r="T93">
-        <v>4.082174527420259</v>
+        <v>4.581896654008704</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.471114790161876</v>
+        <v>5.411646151138378</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.06488692084732051</v>
+        <v>0.06483077064178257</v>
       </c>
       <c r="C94">
-        <v>109.0300083279449</v>
+        <v>107.1971114603113</v>
       </c>
       <c r="D94">
-        <v>375.9040083279448</v>
+        <v>377.0131114603113</v>
       </c>
       <c r="E94">
-        <v>157.064</v>
+        <v>160.006</v>
       </c>
       <c r="F94">
-        <v>270.664</v>
+        <v>273.606</v>
       </c>
       <c r="G94">
         <v>3.79</v>
@@ -8989,28 +8989,28 @@
         <v>81</v>
       </c>
       <c r="M94">
-        <v>14.9677192</v>
+        <v>15.1304118</v>
       </c>
       <c r="N94">
-        <v>66.0322808</v>
+        <v>65.8695882</v>
       </c>
       <c r="O94">
-        <v>12.546133352</v>
+        <v>12.515221758</v>
       </c>
       <c r="P94">
-        <v>53.486147448</v>
+        <v>53.354366442</v>
       </c>
       <c r="Q94">
-        <v>108.986147448</v>
+        <v>108.854366442</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.2959670105915065</v>
+        <v>0.3310468663111797</v>
       </c>
       <c r="T94">
-        <v>4.581896654008704</v>
+        <v>5.224396531050988</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>5.411646151138378</v>
+        <v>5.35345640757775</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.06483077064178257</v>
+        <v>0.06477462043624463</v>
       </c>
       <c r="C95">
-        <v>107.1971114603113</v>
+        <v>105.3707787681304</v>
       </c>
       <c r="D95">
-        <v>377.0131114603113</v>
+        <v>378.1287787681304</v>
       </c>
       <c r="E95">
-        <v>160.006</v>
+        <v>162.948</v>
       </c>
       <c r="F95">
-        <v>273.606</v>
+        <v>276.548</v>
       </c>
       <c r="G95">
         <v>3.79</v>
@@ -9071,28 +9071,28 @@
         <v>81</v>
       </c>
       <c r="M95">
-        <v>15.1304118</v>
+        <v>15.2931044</v>
       </c>
       <c r="N95">
-        <v>65.8695882</v>
+        <v>65.7068956</v>
       </c>
       <c r="O95">
-        <v>12.515221758</v>
+        <v>12.484310164</v>
       </c>
       <c r="P95">
-        <v>53.354366442</v>
+        <v>53.222585436</v>
       </c>
       <c r="Q95">
-        <v>108.854366442</v>
+        <v>108.722585436</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3310468663111797</v>
+        <v>0.3778200072707441</v>
       </c>
       <c r="T95">
-        <v>5.224396531050988</v>
+        <v>6.081063033774035</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>5.35345640757775</v>
+        <v>5.296504743667348</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.06477462043624463</v>
+        <v>0.06471847023070669</v>
       </c>
       <c r="C96">
-        <v>105.3707787681304</v>
+        <v>103.5510686990139</v>
       </c>
       <c r="D96">
-        <v>378.1287787681304</v>
+        <v>379.2510686990138</v>
       </c>
       <c r="E96">
-        <v>162.948</v>
+        <v>165.89</v>
       </c>
       <c r="F96">
-        <v>276.548</v>
+        <v>279.49</v>
       </c>
       <c r="G96">
         <v>3.79</v>
@@ -9153,28 +9153,28 @@
         <v>81</v>
       </c>
       <c r="M96">
-        <v>15.2931044</v>
+        <v>15.455797</v>
       </c>
       <c r="N96">
-        <v>65.7068956</v>
+        <v>65.544203</v>
       </c>
       <c r="O96">
-        <v>12.484310164</v>
+        <v>12.45339857</v>
       </c>
       <c r="P96">
-        <v>53.222585436</v>
+        <v>53.09080443</v>
       </c>
       <c r="Q96">
-        <v>108.722585436</v>
+        <v>108.59080443</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3778200072707441</v>
+        <v>0.4433024046141342</v>
       </c>
       <c r="T96">
-        <v>6.081063033774035</v>
+        <v>7.280396137586302</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.296504743667348</v>
+        <v>5.24075206215506</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.06471847023070669</v>
+        <v>0.06466232002516875</v>
       </c>
       <c r="C97">
-        <v>103.5510686990139</v>
+        <v>101.7380403965313</v>
       </c>
       <c r="D97">
-        <v>379.2510686990138</v>
+        <v>380.3800403965313</v>
       </c>
       <c r="E97">
-        <v>165.89</v>
+        <v>168.8320000000001</v>
       </c>
       <c r="F97">
-        <v>279.49</v>
+        <v>282.432</v>
       </c>
       <c r="G97">
         <v>3.79</v>
@@ -9235,28 +9235,28 @@
         <v>81</v>
       </c>
       <c r="M97">
-        <v>15.455797</v>
+        <v>15.6184896</v>
       </c>
       <c r="N97">
-        <v>65.544203</v>
+        <v>65.3815104</v>
       </c>
       <c r="O97">
-        <v>12.45339857</v>
+        <v>12.422486976</v>
       </c>
       <c r="P97">
-        <v>53.09080443</v>
+        <v>52.95902342399999</v>
       </c>
       <c r="Q97">
-        <v>108.59080443</v>
+        <v>108.459023424</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4433024046141342</v>
+        <v>0.5415260006292194</v>
       </c>
       <c r="T97">
-        <v>7.280396137586302</v>
+        <v>9.079395793304704</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>5.24075206215506</v>
+        <v>5.186160894840945</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.06466232002516875</v>
+        <v>0.0646061698196308</v>
       </c>
       <c r="C98">
-        <v>101.7380403965313</v>
+        <v>99.9317537106005</v>
       </c>
       <c r="D98">
-        <v>380.3800403965313</v>
+        <v>381.5157537106004</v>
       </c>
       <c r="E98">
-        <v>168.832</v>
+        <v>171.774</v>
       </c>
       <c r="F98">
-        <v>282.432</v>
+        <v>285.374</v>
       </c>
       <c r="G98">
         <v>3.79</v>
@@ -9317,28 +9317,28 @@
         <v>81</v>
       </c>
       <c r="M98">
-        <v>15.6184896</v>
+        <v>15.7811822</v>
       </c>
       <c r="N98">
-        <v>65.3815104</v>
+        <v>65.2188178</v>
       </c>
       <c r="O98">
-        <v>12.422486976</v>
+        <v>12.391575382</v>
       </c>
       <c r="P98">
-        <v>52.95902342399999</v>
+        <v>52.827242418</v>
       </c>
       <c r="Q98">
-        <v>108.459023424</v>
+        <v>108.327242418</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5415260006292181</v>
+        <v>0.7052319939876928</v>
       </c>
       <c r="T98">
-        <v>9.079395793304679</v>
+        <v>12.07772855283533</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>5.186160894840945</v>
+        <v>5.132695318605472</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.0646061698196308</v>
+        <v>0.06455001961409287</v>
       </c>
       <c r="C99">
-        <v>99.9317537106005</v>
+        <v>98.13226920806187</v>
       </c>
       <c r="D99">
-        <v>381.5157537106004</v>
+        <v>382.6582692080618</v>
       </c>
       <c r="E99">
-        <v>171.774</v>
+        <v>174.716</v>
       </c>
       <c r="F99">
-        <v>285.374</v>
+        <v>288.316</v>
       </c>
       <c r="G99">
         <v>3.79</v>
@@ -9399,28 +9399,28 @@
         <v>81</v>
       </c>
       <c r="M99">
-        <v>15.7811822</v>
+        <v>15.9438748</v>
       </c>
       <c r="N99">
-        <v>65.2188178</v>
+        <v>65.0561252</v>
       </c>
       <c r="O99">
-        <v>12.391575382</v>
+        <v>12.360663788</v>
       </c>
       <c r="P99">
-        <v>52.827242418</v>
+        <v>52.695461412</v>
       </c>
       <c r="Q99">
-        <v>108.327242418</v>
+        <v>108.195461412</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7052319939876928</v>
+        <v>1.032643980704642</v>
       </c>
       <c r="T99">
-        <v>12.07772855283533</v>
+        <v>18.07439407189664</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>5.132695318605472</v>
+        <v>5.080320876578885</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.06455001961409287</v>
+        <v>0.06449386940855494</v>
       </c>
       <c r="C100">
-        <v>98.13226920806187</v>
+        <v>96.33964818344901</v>
       </c>
       <c r="D100">
-        <v>382.6582692080618</v>
+        <v>383.807648183449</v>
       </c>
       <c r="E100">
-        <v>174.716</v>
+        <v>177.658</v>
       </c>
       <c r="F100">
-        <v>288.316</v>
+        <v>291.258</v>
       </c>
       <c r="G100">
         <v>3.79</v>
@@ -9481,28 +9481,28 @@
         <v>81</v>
       </c>
       <c r="M100">
-        <v>15.9438748</v>
+        <v>16.1065674</v>
       </c>
       <c r="N100">
-        <v>65.0561252</v>
+        <v>64.8934326</v>
       </c>
       <c r="O100">
-        <v>12.360663788</v>
+        <v>12.329752194</v>
       </c>
       <c r="P100">
-        <v>52.695461412</v>
+        <v>52.563680406</v>
       </c>
       <c r="Q100">
-        <v>108.195461412</v>
+        <v>108.063680406</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.032643980704642</v>
+        <v>2.01487994085549</v>
       </c>
       <c r="T100">
-        <v>18.07439407189664</v>
+        <v>36.06439062908058</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>5.080320876578885</v>
+        <v>5.029004504088189</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.06449386940855494</v>
-      </c>
-      <c r="C101">
-        <v>96.33964818344901</v>
-      </c>
-      <c r="D101">
-        <v>383.807648183449</v>
-      </c>
-      <c r="E101">
-        <v>177.658</v>
-      </c>
-      <c r="F101">
-        <v>291.258</v>
-      </c>
-      <c r="G101">
-        <v>3.79</v>
-      </c>
-      <c r="H101">
-        <v>180.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>136.5</v>
-      </c>
-      <c r="K101">
-        <v>55.5</v>
-      </c>
-      <c r="L101">
-        <v>81</v>
-      </c>
-      <c r="M101">
-        <v>16.1065674</v>
-      </c>
-      <c r="N101">
-        <v>64.8934326</v>
-      </c>
-      <c r="O101">
-        <v>12.329752194</v>
-      </c>
-      <c r="P101">
-        <v>52.563680406</v>
-      </c>
-      <c r="Q101">
-        <v>108.063680406</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.01487994085549</v>
-      </c>
-      <c r="T101">
-        <v>36.06439062908058</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.19</v>
-      </c>
-      <c r="W101">
-        <v>0.04479300000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.029004504088189</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
